--- a/Data Set/Teamsync_new_testcases.backup.xlsx
+++ b/Data Set/Teamsync_new_testcases.backup.xlsx
@@ -405,7 +405,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -692,6 +692,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6346,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="17.08984375" bestFit="1" customWidth="1" style="29" min="1" max="1"/>
@@ -6441,6 +6445,8 @@
       </c>
       <c r="B7" s="49" t="n"/>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10" ht="31" customHeight="1" s="29">
       <c r="A10" s="54" t="inlineStr">
         <is>
@@ -6568,9 +6574,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="41" t="inlineStr">
+      <c r="K12" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M12" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:20 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -6617,9 +6633,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="41" t="inlineStr">
+      <c r="K13" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M13" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:20 (0.15s)</t>
         </is>
       </c>
     </row>
@@ -6666,9 +6692,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L14" s="107" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request | AssertionError: [API] Expected 200, got 400</t>
+        </is>
+      </c>
+      <c r="M14" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:20 (0.23s)</t>
         </is>
       </c>
     </row>
@@ -6715,9 +6751,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="41" t="inlineStr">
+      <c r="K15" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M15" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:21 (0.23s)</t>
         </is>
       </c>
     </row>
@@ -6764,9 +6810,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="41" t="inlineStr">
+      <c r="K16" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M16" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:23 (2.21s)</t>
         </is>
       </c>
     </row>
@@ -6813,9 +6869,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K17" s="41" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="K17" s="104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="M17" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:23 (0.46s)</t>
         </is>
       </c>
     </row>
@@ -6862,9 +6928,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="41" t="inlineStr">
+      <c r="K18" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M18" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:26 (2.76s)</t>
         </is>
       </c>
     </row>
@@ -6911,9 +6987,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="41" t="inlineStr">
+      <c r="K19" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M19" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:30 (3.63s)</t>
         </is>
       </c>
     </row>
@@ -6960,9 +7046,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="41" t="inlineStr">
+      <c r="K20" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 0</t>
+        </is>
+      </c>
+      <c r="M20" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:35 (4.89s)</t>
         </is>
       </c>
     </row>
@@ -7009,9 +7105,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="41" t="inlineStr">
+      <c r="K21" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M21" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:39 (4.65s)</t>
         </is>
       </c>
     </row>
@@ -7058,9 +7164,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="41" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="K22" s="104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 404 Not Found</t>
+        </is>
+      </c>
+      <c r="M22" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:39 (0.13s)</t>
         </is>
       </c>
     </row>
@@ -7107,9 +7223,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="K23" s="106" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L23" s="107" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request | AssertionError: [API] Bulk move failed: 400</t>
+        </is>
+      </c>
+      <c r="M23" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:40 (0.24s)</t>
         </is>
       </c>
     </row>
@@ -7156,9 +7282,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="41" t="inlineStr">
+      <c r="K24" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M24" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:23:42 (2.27s)</t>
         </is>
       </c>
     </row>
@@ -7214,6 +7350,8 @@
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="11" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="31" customHeight="1" s="29">
       <c r="A31" s="51" t="inlineStr">
         <is>
@@ -7236,6 +7374,9 @@
           <t>Total Test Cases</t>
         </is>
       </c>
+      <c r="K31" s="76" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" ht="31" customHeight="1" s="29">
       <c r="B32" s="51" t="inlineStr">
@@ -7249,7 +7390,9 @@
           <t>Executed Test Cases</t>
         </is>
       </c>
-      <c r="K32" s="53" t="n"/>
+      <c r="K32" s="77" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="33" ht="31" customHeight="1" s="29">
       <c r="B33" s="51" t="inlineStr">
@@ -7263,7 +7406,9 @@
           <t>Passed Test Cases</t>
         </is>
       </c>
-      <c r="K33" s="53" t="n"/>
+      <c r="K33" s="77" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34" ht="31" customHeight="1" s="29">
       <c r="B34" s="51" t="inlineStr">
@@ -7277,7 +7422,9 @@
           <t>Failed Test Cases</t>
         </is>
       </c>
-      <c r="K34" s="53" t="n"/>
+      <c r="K34" s="77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" ht="31" customHeight="1" s="29">
       <c r="B35" s="51" t="inlineStr">
@@ -7291,7 +7438,9 @@
           <t>Blocked Test Cases</t>
         </is>
       </c>
-      <c r="K35" s="53" t="n"/>
+      <c r="K35" s="77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="46.5" customHeight="1" s="29">
       <c r="B36" s="51" t="inlineStr">
@@ -7305,8 +7454,14 @@
           <t>Not Executed Test Cases</t>
         </is>
       </c>
-      <c r="K36" s="53" t="n"/>
-    </row>
+      <c r="K36" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10220,10 +10375,7 @@
       </c>
       <c r="B7" s="49" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10" ht="31" customHeight="1" s="29"/>
-    <row r="11"/>
     <row r="12" ht="15.5" customHeight="1" s="29">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -10365,7 +10517,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:28 (3.02s)</t>
+          <t>2026-05-21 14:31:13 (4.74s)</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10576,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:31 (1.13s)</t>
+          <t>2026-05-21 14:31:16 (1.05s)</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10635,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:33 (1.00s)</t>
+          <t>2026-05-21 14:31:19 (0.93s)</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10694,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:35 (0.00s)</t>
+          <t>2026-05-21 14:31:20 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10753,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:38 (2.99s)</t>
+          <t>2026-05-21 14:31:22 (2.60s)</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10812,7 @@
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:53 (4.09s)</t>
+          <t>2026-05-21 14:31:36 (3.79s)</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10871,7 @@
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:05:57 (4.10s)</t>
+          <t>2026-05-21 14:31:40 (3.77s)</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10930,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:00 (3.00s)</t>
+          <t>2026-05-21 14:31:43 (2.59s)</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10989,7 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:03 (3.11s)</t>
+          <t>2026-05-21 14:31:45 (2.68s)</t>
         </is>
       </c>
     </row>
@@ -10896,7 +11048,7 @@
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:06 (2.94s)</t>
+          <t>2026-05-21 14:31:48 (2.63s)</t>
         </is>
       </c>
     </row>
@@ -10955,7 +11107,7 @@
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:09 (2.94s)</t>
+          <t>2026-05-21 14:31:51 (2.66s)</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11166,7 @@
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:09 (0.00s)</t>
+          <t>2026-05-21 14:31:51 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11225,7 @@
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:13 (4.19s)</t>
+          <t>2026-05-21 14:31:55 (3.86s)</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11280,7 @@
       <c r="L27" s="93" t="inlineStr"/>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:15 (0.64s)</t>
+          <t>2026-05-21 14:31:56 (0.41s)</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11335,7 @@
       <c r="L28" s="93" t="inlineStr"/>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:15 (0.60s)</t>
+          <t>2026-05-21 14:31:56 (0.37s)</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11390,7 @@
       <c r="L29" s="93" t="inlineStr"/>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:16 (0.67s)</t>
+          <t>2026-05-21 14:31:56 (0.34s)</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11445,7 @@
       <c r="L30" s="93" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:17 (1.28s)</t>
+          <t>2026-05-21 14:31:57 (0.93s)</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11504,7 @@
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:22 (4.33s)</t>
+          <t>2026-05-21 14:32:01 (3.75s)</t>
         </is>
       </c>
     </row>
@@ -11411,11 +11563,10 @@
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:23 (1.21s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t>2026-05-21 14:32:02 (0.90s)</t>
+        </is>
+      </c>
+    </row>
     <row r="34" ht="29" customHeight="1" s="29"/>
     <row r="35" ht="29" customHeight="1" s="29">
       <c r="D35" s="44" t="inlineStr">
@@ -11538,8 +11689,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="24" t="n"/>
     </row>
@@ -11670,7 +11819,6 @@
       </c>
       <c r="B7" s="49" t="n"/>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="N9" s="1" t="n"/>
     </row>
@@ -11822,7 +11970,7 @@
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:46 (8.51s)</t>
+          <t>2026-05-21 14:32:23 (8.01s)</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -11887,7 +12035,7 @@
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:06:54 (8.71s)</t>
+          <t>2026-05-21 14:32:31 (8.41s)</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -11952,7 +12100,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:07:02 (8.09s)</t>
+          <t>2026-05-21 14:32:40 (8.45s)</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -12017,7 +12165,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:07:10 (7.90s)</t>
+          <t>2026-05-21 14:32:48 (7.87s)</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -12082,7 +12230,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:07:19 (8.58s)</t>
+          <t>2026-05-21 14:32:56 (7.91s)</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -12142,7 +12290,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:07:36 (17.51s)</t>
+          <t>2026-05-21 14:33:12 (16.87s)</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -12202,7 +12350,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:09:05 (87.89s)</t>
+          <t>2026-05-21 14:34:45 (92.59s)</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -12262,7 +12410,7 @@
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:09:23 (18.41s)</t>
+          <t>2026-05-21 14:35:04 (18.38s)</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -12317,12 +12465,12 @@
       </c>
       <c r="L20" s="98" t="inlineStr">
         <is>
-          <t>AssertionError: [UI→API] single file upload — no upload response was captured</t>
+          <t>HTTP 400 Bad Request | AssertionError: [UI→API] single file upload — expected 200, got 400</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:09:42 (18.67s)</t>
+          <t>2026-05-21 14:35:23 (18.71s)</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -12382,7 +12530,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:10:00 (17.70s)</t>
+          <t>2026-05-21 14:36:42 (79.31s)</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -12442,7 +12590,7 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:10:18 (18.13s)</t>
+          <t>2026-05-21 14:37:00 (17.87s)</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -12502,7 +12650,7 @@
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:10:36 (17.63s)</t>
+          <t>2026-05-21 14:37:17 (17.50s)</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -12562,7 +12710,7 @@
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:11:57 (81.56s)</t>
+          <t>2026-05-21 14:38:38 (80.44s)</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
@@ -12622,7 +12770,7 @@
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:12:16 (18.46s)</t>
+          <t>2026-05-21 14:38:56 (18.31s)</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -12682,7 +12830,7 @@
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:12:35 (19.39s)</t>
+          <t>2026-05-21 14:39:14 (18.22s)</t>
         </is>
       </c>
       <c r="N26" s="11" t="n"/>
@@ -12742,7 +12890,7 @@
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:14:24 (108.50s)</t>
+          <t>2026-05-21 14:40:50 (95.49s)</t>
         </is>
       </c>
       <c r="N27" s="11" t="n"/>
@@ -12802,7 +12950,7 @@
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:14:36 (11.77s)</t>
+          <t>2026-05-21 14:40:57 (6.84s)</t>
         </is>
       </c>
       <c r="N28" s="11" t="n"/>
@@ -12862,7 +13010,7 @@
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:14:37 (0.25s)</t>
+          <t>2026-05-21 14:40:58 (0.28s)</t>
         </is>
       </c>
       <c r="N29" s="11" t="n"/>
@@ -12918,7 +13066,7 @@
       <c r="L30" s="96" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:15:10 (33.57s)</t>
+          <t>2026-05-21 14:41:29 (30.78s)</t>
         </is>
       </c>
       <c r="N30" s="11" t="n"/>
@@ -12978,7 +13126,7 @@
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:16:48 (97.81s)</t>
+          <t>2026-05-21 14:43:01 (92.44s)</t>
         </is>
       </c>
       <c r="N31" s="11" t="n"/>
@@ -13038,7 +13186,7 @@
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:16:48 (0.00s)</t>
+          <t>2026-05-21 14:43:01 (0.00s)</t>
         </is>
       </c>
       <c r="N32" s="11" t="n"/>
@@ -13098,7 +13246,7 @@
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:17:07 (18.46s)</t>
+          <t>2026-05-21 14:43:20 (18.36s)</t>
         </is>
       </c>
       <c r="N33" s="11" t="n"/>
@@ -13158,7 +13306,7 @@
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:17:26 (18.70s)</t>
+          <t>2026-05-21 14:43:38 (18.70s)</t>
         </is>
       </c>
       <c r="N34" s="11" t="n"/>
@@ -13218,7 +13366,7 @@
       </c>
       <c r="M35" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:17:26 (0.09s)</t>
+          <t>2026-05-21 14:43:39 (0.18s)</t>
         </is>
       </c>
       <c r="N35" s="11" t="n"/>
@@ -13278,7 +13426,7 @@
       </c>
       <c r="M36" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:49 (83.00s)</t>
+          <t>2026-05-21 14:45:01 (81.95s)</t>
         </is>
       </c>
       <c r="N36" s="11" t="n"/>
@@ -13338,7 +13486,7 @@
       </c>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:52 (2.64s)</t>
+          <t>2026-05-21 14:45:04 (3.15s)</t>
         </is>
       </c>
       <c r="N37" s="11" t="n"/>
@@ -13398,7 +13546,7 @@
       </c>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:52 (0.34s)</t>
+          <t>2026-05-21 14:45:04 (0.16s)</t>
         </is>
       </c>
       <c r="N38" s="11" t="n"/>
@@ -13458,7 +13606,7 @@
       </c>
       <c r="M39" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:53 (0.28s)</t>
+          <t>2026-05-21 14:45:05 (0.20s)</t>
         </is>
       </c>
       <c r="N39" s="11" t="n"/>
@@ -13518,7 +13666,7 @@
       </c>
       <c r="M40" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:53 (0.27s)</t>
+          <t>2026-05-21 14:45:05 (0.16s)</t>
         </is>
       </c>
       <c r="N40" s="11" t="n"/>
@@ -13578,7 +13726,7 @@
       </c>
       <c r="M41" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:53 (0.34s)</t>
+          <t>2026-05-21 14:45:05 (0.28s)</t>
         </is>
       </c>
       <c r="N41" s="11" t="n"/>
@@ -13639,7 +13787,7 @@
       </c>
       <c r="M42" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:54 (0.38s)</t>
+          <t>2026-05-21 14:45:06 (0.22s)</t>
         </is>
       </c>
       <c r="N42" s="11" t="n"/>
@@ -13699,7 +13847,7 @@
       </c>
       <c r="M43" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:18:58 (3.77s)</t>
+          <t>2026-05-21 14:45:10 (3.73s)</t>
         </is>
       </c>
       <c r="N43" s="11" t="n"/>
@@ -13759,7 +13907,7 @@
       </c>
       <c r="M44" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:01 (2.87s)</t>
+          <t>2026-05-21 14:45:24 (14.32s)</t>
         </is>
       </c>
       <c r="N44" s="11" t="n"/>
@@ -13819,7 +13967,7 @@
       </c>
       <c r="M45" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:01 (0.00s)</t>
+          <t>2026-05-21 14:45:24 (0.00s)</t>
         </is>
       </c>
       <c r="N45" s="11" t="n"/>
@@ -13879,7 +14027,7 @@
       </c>
       <c r="M46" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:01 (0.00s)</t>
+          <t>2026-05-21 14:45:24 (0.00s)</t>
         </is>
       </c>
       <c r="N46" s="11" t="n"/>
@@ -13939,7 +14087,7 @@
       </c>
       <c r="M47" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:01 (0.00s)</t>
+          <t>2026-05-21 14:45:24 (0.00s)</t>
         </is>
       </c>
       <c r="N47" s="11" t="n"/>
@@ -13999,7 +14147,7 @@
       </c>
       <c r="M48" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:02 (0.51s)</t>
+          <t>2026-05-21 14:45:25 (0.53s)</t>
         </is>
       </c>
       <c r="N48" s="11" t="n"/>
@@ -14059,7 +14207,7 @@
       </c>
       <c r="M49" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:02 (0.00s)</t>
+          <t>2026-05-21 14:45:25 (0.00s)</t>
         </is>
       </c>
       <c r="N49" s="11" t="n"/>
@@ -14119,7 +14267,7 @@
       </c>
       <c r="M50" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:02 (0.63s)</t>
+          <t>2026-05-21 14:45:26 (0.20s)</t>
         </is>
       </c>
       <c r="N50" s="11" t="n"/>
@@ -14179,7 +14327,7 @@
       </c>
       <c r="M51" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:03 (0.71s)</t>
+          <t>2026-05-21 14:45:26 (0.69s)</t>
         </is>
       </c>
       <c r="N51" s="11" t="n"/>
@@ -14239,7 +14387,7 @@
       </c>
       <c r="M52" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:03 (0.00s)</t>
+          <t>2026-05-21 14:45:26 (0.00s)</t>
         </is>
       </c>
       <c r="N52" s="11" t="n"/>
@@ -14299,7 +14447,7 @@
       </c>
       <c r="M53" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:03 (0.00s)</t>
+          <t>2026-05-21 14:45:26 (0.00s)</t>
         </is>
       </c>
       <c r="N53" s="11" t="n"/>
@@ -14359,7 +14507,7 @@
       </c>
       <c r="M54" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:03 (0.00s)</t>
+          <t>2026-05-21 14:45:26 (0.00s)</t>
         </is>
       </c>
       <c r="N54" s="11" t="n"/>
@@ -14419,7 +14567,7 @@
       </c>
       <c r="M55" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:04 (0.20s)</t>
+          <t>2026-05-21 14:45:27 (0.17s)</t>
         </is>
       </c>
       <c r="N55" s="11" t="n"/>
@@ -14479,7 +14627,7 @@
       </c>
       <c r="M56" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:04 (0.00s)</t>
+          <t>2026-05-21 14:45:27 (0.00s)</t>
         </is>
       </c>
       <c r="N56" s="11" t="n"/>
@@ -14539,7 +14687,7 @@
       </c>
       <c r="M57" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:04 (0.01s)</t>
+          <t>2026-05-21 14:45:27 (0.00s)</t>
         </is>
       </c>
       <c r="N57" s="11" t="n"/>
@@ -14599,7 +14747,7 @@
       </c>
       <c r="M58" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:24 (20.22s)</t>
+          <t>2026-05-21 14:45:47 (20.01s)</t>
         </is>
       </c>
       <c r="N58" s="11" t="n"/>
@@ -14659,7 +14807,7 @@
       </c>
       <c r="M59" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:44 (19.94s)</t>
+          <t>2026-05-21 14:46:07 (19.94s)</t>
         </is>
       </c>
       <c r="N59" s="11" t="n"/>
@@ -14719,7 +14867,7 @@
       </c>
       <c r="M60" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:44 (0.00s)</t>
+          <t>2026-05-21 14:46:07 (0.00s)</t>
         </is>
       </c>
       <c r="N60" s="11" t="n"/>
@@ -14779,7 +14927,7 @@
       </c>
       <c r="M61" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:44 (0.43s)</t>
+          <t>2026-05-21 14:46:08 (0.65s)</t>
         </is>
       </c>
       <c r="N61" s="11" t="n"/>
@@ -14839,7 +14987,7 @@
       </c>
       <c r="M62" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:45 (0.66s)</t>
+          <t>2026-05-21 14:46:08 (0.51s)</t>
         </is>
       </c>
       <c r="N62" s="11" t="n"/>
@@ -14899,7 +15047,7 @@
       </c>
       <c r="M63" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:46 (0.21s)</t>
+          <t>2026-05-21 14:46:09 (0.25s)</t>
         </is>
       </c>
       <c r="N63" s="11" t="n"/>
@@ -14959,7 +15107,7 @@
       </c>
       <c r="M64" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:46 (0.54s)</t>
+          <t>2026-05-21 14:46:09 (0.41s)</t>
         </is>
       </c>
       <c r="N64" s="11" t="n"/>
@@ -15019,7 +15167,7 @@
       </c>
       <c r="M65" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:47 (0.67s)</t>
+          <t>2026-05-21 14:46:10 (0.68s)</t>
         </is>
       </c>
       <c r="N65" s="11" t="n"/>
@@ -15079,7 +15227,7 @@
       </c>
       <c r="M66" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:48 (0.74s)</t>
+          <t>2026-05-21 14:46:11 (0.51s)</t>
         </is>
       </c>
       <c r="N66" s="11" t="n"/>
@@ -15139,7 +15287,7 @@
       </c>
       <c r="M67" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:49 (1.17s)</t>
+          <t>2026-05-21 14:46:12 (1.22s)</t>
         </is>
       </c>
       <c r="N67" s="11" t="n"/>
@@ -15195,7 +15343,7 @@
       <c r="L68" s="96" t="inlineStr"/>
       <c r="M68" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:49 (0.01s)</t>
+          <t>2026-05-21 14:46:12 (0.01s)</t>
         </is>
       </c>
       <c r="N68" s="11" t="n"/>
@@ -15255,7 +15403,7 @@
       </c>
       <c r="M69" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:49 (0.00s)</t>
+          <t>2026-05-21 14:46:12 (0.00s)</t>
         </is>
       </c>
       <c r="N69" s="11" t="n"/>
@@ -15315,7 +15463,7 @@
       </c>
       <c r="M70" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:49 (0.00s)</t>
+          <t>2026-05-21 14:46:12 (0.00s)</t>
         </is>
       </c>
       <c r="N70" s="11" t="n"/>
@@ -15371,7 +15519,7 @@
       <c r="L71" s="96" t="inlineStr"/>
       <c r="M71" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:52 (2.51s)</t>
+          <t>2026-05-21 14:46:15 (2.60s)</t>
         </is>
       </c>
       <c r="N71" s="11" t="n"/>
@@ -15431,7 +15579,7 @@
       </c>
       <c r="M72" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:52 (0.00s)</t>
+          <t>2026-05-21 14:46:15 (0.00s)</t>
         </is>
       </c>
       <c r="N72" s="11" t="n"/>
@@ -15491,7 +15639,7 @@
       </c>
       <c r="M73" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:19:55 (2.81s)</t>
+          <t>2026-05-21 14:46:18 (3.08s)</t>
         </is>
       </c>
       <c r="N73" s="11" t="n"/>
@@ -15551,7 +15699,7 @@
       </c>
       <c r="M74" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:20:15 (20.01s)</t>
+          <t>2026-05-21 14:46:38 (19.90s)</t>
         </is>
       </c>
       <c r="N74" s="11" t="n"/>
@@ -15611,7 +15759,7 @@
       </c>
       <c r="M75" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:20:35 (19.77s)</t>
+          <t>2026-05-21 14:46:58 (19.91s)</t>
         </is>
       </c>
       <c r="N75" s="11" t="n"/>
@@ -15671,7 +15819,7 @@
       </c>
       <c r="M76" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:20:52 (16.95s)</t>
+          <t>2026-05-21 14:47:15 (16.91s)</t>
         </is>
       </c>
       <c r="N76" s="11" t="n"/>
@@ -15731,7 +15879,7 @@
       </c>
       <c r="M77" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:20:52 (0.00s)</t>
+          <t>2026-05-21 14:47:15 (0.00s)</t>
         </is>
       </c>
       <c r="N77" s="11" t="n"/>
@@ -15791,13 +15939,11 @@
       </c>
       <c r="M78" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:20:52 (0.00s)</t>
+          <t>2026-05-21 14:47:15 (0.00s)</t>
         </is>
       </c>
       <c r="N78" s="11" t="n"/>
     </row>
-    <row r="79"/>
-    <row r="80"/>
     <row r="81">
       <c r="B81" s="44" t="inlineStr">
         <is>
@@ -15914,32 +16060,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
     <row r="113" ht="15.5" customHeight="1" s="29">
       <c r="K113" s="53" t="n"/>
     </row>
@@ -15971,7 +16091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" customWidth="1" style="29" min="1" max="1"/>
@@ -16211,12 +16331,12 @@
       </c>
       <c r="L12" s="101" t="inlineStr">
         <is>
-          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_dbfea7da' did not appear in the file manager</t>
+          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_66399160' did not appear in the file manager</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:25 (21.20s)</t>
+          <t>2026-05-21 14:47:48 (21.15s)</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16395,7 @@
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:25 (0.20s)</t>
+          <t>2026-05-21 14:47:48 (0.32s)</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16454,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:26 (0.60s)</t>
+          <t>2026-05-21 14:47:49 (0.67s)</t>
         </is>
       </c>
     </row>
@@ -16393,7 +16513,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:27 (0.23s)</t>
+          <t>2026-05-21 14:47:50 (0.35s)</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16572,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:27 (0.38s)</t>
+          <t>2026-05-21 14:47:50 (0.33s)</t>
         </is>
       </c>
     </row>
@@ -16511,7 +16631,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:31 (3.15s)</t>
+          <t>2026-05-21 14:47:53 (3.04s)</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16690,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:31 (0.24s)</t>
+          <t>2026-05-21 14:47:54 (0.18s)</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16749,7 @@
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:31 (0.00s)</t>
+          <t>2026-05-21 14:47:54 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16688,7 +16808,7 @@
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (7.94s)</t>
+          <t>2026-05-21 14:48:02 (8.33s)</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16867,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16926,7 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16985,7 @@
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16924,7 +17044,7 @@
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16983,7 +17103,7 @@
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17162,7 @@
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17221,7 @@
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17280,7 @@
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17339,7 @@
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17398,7 @@
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17457,7 @@
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17516,7 @@
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17575,7 @@
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17634,7 @@
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:21:39 (0.00s)</t>
+          <t>2026-05-21 14:48:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17524,8 +17644,6 @@
     <row r="36">
       <c r="B36" s="16" t="n"/>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="15.5" customHeight="1" s="29">
       <c r="A39" s="51" t="inlineStr">
         <is>
@@ -17632,10 +17750,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17648,7 +17762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" customWidth="1" style="29" min="1" max="1"/>
@@ -17741,8 +17855,6 @@
       </c>
       <c r="B7" s="49" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10" ht="15.5" customHeight="1" s="29">
       <c r="A10" s="54" t="inlineStr">
         <is>
@@ -17884,7 +17996,7 @@
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:10 (18.79s)</t>
+          <t>2026-05-21 14:48:32 (18.49s)</t>
         </is>
       </c>
     </row>
@@ -17943,7 +18055,7 @@
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:16 (5.84s)</t>
+          <t>2026-05-21 14:48:38 (5.01s)</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18114,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:22:49 (32.50s)</t>
+          <t>2026-05-21 14:49:07 (29.28s)</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18173,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:00 (11.13s)</t>
+          <t>2026-05-21 14:49:17 (9.65s)</t>
         </is>
       </c>
     </row>
@@ -18116,7 +18228,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:10 (10.28s)</t>
+          <t>2026-05-21 14:49:26 (9.37s)</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18287,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:23 (13.01s)</t>
+          <t>2026-05-21 14:50:08 (41.69s)</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18346,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:33 (9.78s)</t>
+          <t>2026-05-21 14:50:18 (10.13s)</t>
         </is>
       </c>
     </row>
@@ -18293,7 +18405,7 @@
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:47 (14.43s)</t>
+          <t>2026-05-21 14:50:30 (12.05s)</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18464,7 @@
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:57 (9.78s)</t>
+          <t>2026-05-21 14:50:40 (9.75s)</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18523,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:58 (0.18s)</t>
+          <t>2026-05-21 14:50:40 (0.18s)</t>
         </is>
       </c>
     </row>
@@ -18470,12 +18582,10 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:23:58 (0.00s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
+          <t>2026-05-21 14:50:40 (0.00s)</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="15.5" customHeight="1" s="29">
       <c r="A25" s="51" t="inlineStr">
         <is>
@@ -18582,10 +18692,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18597,7 +18703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" customWidth="1" style="29" min="1" max="1"/>
@@ -18690,7 +18796,6 @@
       <c r="B7" s="49" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1" s="29"/>
-    <row r="9"/>
     <row r="10" ht="29" customHeight="1" s="29">
       <c r="A10" s="54" t="inlineStr">
         <is>
@@ -18828,7 +18933,7 @@
       </c>
       <c r="M12" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:15 (2.07s)</t>
+          <t>2026-05-21 14:50:57 (1.92s)</t>
         </is>
       </c>
     </row>
@@ -18886,7 +18991,7 @@
       </c>
       <c r="M13" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:18 (1.97s)</t>
+          <t>2026-05-21 14:50:59 (1.86s)</t>
         </is>
       </c>
     </row>
@@ -18944,7 +19049,7 @@
       </c>
       <c r="M14" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:20 (2.07s)</t>
+          <t>2026-05-21 14:51:01 (1.86s)</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19107,7 @@
       </c>
       <c r="M15" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:22 (2.00s)</t>
+          <t>2026-05-21 14:51:03 (1.92s)</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19165,7 @@
       </c>
       <c r="M16" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:26 (4.13s)</t>
+          <t>2026-05-21 14:51:07 (3.94s)</t>
         </is>
       </c>
     </row>
@@ -19118,7 +19223,7 @@
       </c>
       <c r="M17" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:30 (3.57s)</t>
+          <t>2026-05-21 14:51:10 (3.55s)</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19281,7 @@
       </c>
       <c r="M18" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:35 (5.40s)</t>
+          <t>2026-05-21 14:51:15 (4.41s)</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19339,7 @@
       </c>
       <c r="M19" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:37 (2.03s)</t>
+          <t>2026-05-21 14:51:17 (1.91s)</t>
         </is>
       </c>
     </row>
@@ -19292,7 +19397,7 @@
       </c>
       <c r="M20" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:42 (4.41s)</t>
+          <t>2026-05-21 14:51:21 (4.27s)</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19451,7 @@
       <c r="L21" s="105" t="inlineStr"/>
       <c r="M21" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:24:55 (13.11s)</t>
+          <t>2026-05-21 14:51:34 (12.90s)</t>
         </is>
       </c>
     </row>
@@ -19400,7 +19505,7 @@
       <c r="L22" s="105" t="inlineStr"/>
       <c r="M22" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:25:08 (12.88s)</t>
+          <t>2026-05-21 14:51:47 (12.81s)</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19563,7 @@
       </c>
       <c r="M23" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:25:12 (3.97s)</t>
+          <t>2026-05-21 14:51:51 (3.83s)</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19621,7 @@
       </c>
       <c r="M24" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:25:16 (3.94s)</t>
+          <t>2026-05-21 14:51:55 (4.00s)</t>
         </is>
       </c>
     </row>
@@ -19574,12 +19679,10 @@
       </c>
       <c r="M25" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:25:24 (7.79s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+          <t>2026-05-21 14:52:02 (7.33s)</t>
+        </is>
+      </c>
+    </row>
     <row r="28" ht="31" customHeight="1" s="29">
       <c r="A28" s="51" t="inlineStr">
         <is>
@@ -19685,10 +19788,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Data Set/Teamsync_new_testcases.backup.xlsx
+++ b/Data Set/Teamsync_new_testcases.backup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6830" tabRatio="600" firstSheet="6" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6830" tabRatio="600" firstSheet="4" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,12 +15,13 @@
     <sheet name="Rename" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Move" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Create Shortcut" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TAG-Phase2" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="DBtalk - Phase2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Tag" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DBtalk " sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="RBAC" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Share" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Trash" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Version &amp; Compare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Advance search" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,6 +145,43 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF9C5700"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
@@ -163,7 +201,7 @@
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -255,6 +293,38 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -398,7 +468,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -647,69 +717,109 @@
     <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7772,15 +7882,15 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr"/>
+      <c r="L12" s="130" t="inlineStr"/>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:06 (4.59s)</t>
+          <t>2026-06-18 10:16:49 (4.23s)</t>
         </is>
       </c>
     </row>
@@ -7827,19 +7937,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:07 (0.92s)</t>
+          <t>2026-06-18 10:16:50 (0.92s)</t>
         </is>
       </c>
     </row>
@@ -7886,19 +7996,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:10 (2.96s)</t>
+          <t>2026-06-18 10:16:53 (2.84s)</t>
         </is>
       </c>
     </row>
@@ -7945,19 +8055,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:11 (0.88s)</t>
+          <t>2026-06-18 10:16:54 (0.86s)</t>
         </is>
       </c>
     </row>
@@ -8004,19 +8114,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:12 (1.27s)</t>
+          <t>2026-06-18 10:16:55 (1.13s)</t>
         </is>
       </c>
     </row>
@@ -8063,19 +8173,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:13 (1.03s)</t>
+          <t>2026-06-18 10:16:56 (0.96s)</t>
         </is>
       </c>
     </row>
@@ -8122,19 +8232,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:14 (0.96s)</t>
+          <t>2026-06-18 10:16:57 (0.98s)</t>
         </is>
       </c>
     </row>
@@ -8181,19 +8291,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:15 (0.97s)</t>
+          <t>2026-06-18 10:16:58 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -8240,19 +8350,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:16 (0.91s)</t>
+          <t>2026-06-18 10:16:59 (0.94s)</t>
         </is>
       </c>
     </row>
@@ -8299,19 +8409,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr">
+      <c r="L21" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:17 (1.13s)</t>
+          <t>2026-06-18 10:17:00 (1.10s)</t>
         </is>
       </c>
     </row>
@@ -8358,19 +8468,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="105" t="inlineStr">
+      <c r="L22" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:19 (1.13s)</t>
+          <t>2026-06-18 10:17:01 (1.12s)</t>
         </is>
       </c>
     </row>
@@ -8417,19 +8527,19 @@
           <t>409 Conflict – Duplicate resource</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="105" t="inlineStr">
+      <c r="L23" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:20 (1.21s)</t>
+          <t>2026-06-18 10:17:03 (1.19s)</t>
         </is>
       </c>
     </row>
@@ -8476,19 +8586,19 @@
           <t>400 Bad Request – Missing required input</t>
         </is>
       </c>
-      <c r="K24" s="108" t="inlineStr">
+      <c r="K24" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L24" s="109" t="inlineStr">
+      <c r="L24" s="132" t="inlineStr">
         <is>
           <t>HTTP 200 OK | AssertionError: [API] Expected 400/422 for empty usernames, got 200</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:21 (1.01s)</t>
+          <t>2026-06-18 10:17:03 (0.87s)</t>
         </is>
       </c>
     </row>
@@ -8535,19 +8645,19 @@
           <t>400 Bad Request – Invalid input format</t>
         </is>
       </c>
-      <c r="K25" s="108" t="inlineStr">
+      <c r="K25" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L25" s="109" t="inlineStr">
+      <c r="L25" s="132" t="inlineStr">
         <is>
           <t>HTTP 200 OK | AssertionError: [API] Expected 400/422 for invalid email, got 200</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:22 (1.16s)</t>
+          <t>2026-06-18 10:17:04 (0.91s)</t>
         </is>
       </c>
     </row>
@@ -8594,19 +8704,19 @@
           <t>403 Forbidden – Action not allowed</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="105" t="inlineStr">
+      <c r="L26" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:23 (0.95s)</t>
+          <t>2026-06-18 10:17:05 (0.88s)</t>
         </is>
       </c>
     </row>
@@ -8653,19 +8763,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K27" s="106" t="inlineStr">
+      <c r="K27" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L27" s="107" t="inlineStr">
+      <c r="L27" s="131" t="inlineStr">
         <is>
           <t>Skipped: Skipped per project decision — server JVM heap is limited; large-file scenarios are tested by Upload module</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:23 (0.00s)</t>
+          <t>2026-06-18 10:17:05 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -8712,19 +8822,19 @@
           <t>400 Bad Request – Invalid filename</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="105" t="inlineStr">
+      <c r="L28" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:26 (2.49s)</t>
+          <t>2026-06-18 10:17:08 (2.43s)</t>
         </is>
       </c>
     </row>
@@ -8771,19 +8881,19 @@
           <t>503 Service Unavailable – Network/server issue</t>
         </is>
       </c>
-      <c r="K29" s="106" t="inlineStr">
+      <c r="K29" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L29" s="107" t="inlineStr">
+      <c r="L29" s="131" t="inlineStr">
         <is>
           <t>Skipped: Hard to simulate true network failure deterministically — would need a proxy/middleware that drops connections</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:26 (0.00s)</t>
+          <t>2026-06-18 10:17:08 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -8830,19 +8940,19 @@
           <t>401 Unauthorized – Authentication required</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="105" t="inlineStr">
+      <c r="L30" s="130" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:26 (0.83s)</t>
+          <t>2026-06-18 10:17:09 (0.79s)</t>
         </is>
       </c>
     </row>
@@ -8889,19 +8999,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K31" s="104" t="inlineStr">
+      <c r="K31" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L31" s="105" t="inlineStr">
+      <c r="L31" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:28 (1.24s)</t>
+          <t>2026-06-18 10:17:10 (1.22s)</t>
         </is>
       </c>
     </row>
@@ -8948,19 +9058,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K32" s="104" t="inlineStr">
+      <c r="K32" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L32" s="105" t="inlineStr">
+      <c r="L32" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:30 (2.57s)</t>
+          <t>2026-06-18 10:17:12 (2.55s)</t>
         </is>
       </c>
     </row>
@@ -9007,19 +9117,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K33" s="106" t="inlineStr">
+      <c r="K33" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L33" s="107" t="inlineStr">
+      <c r="L33" s="131" t="inlineStr">
         <is>
           <t>Skipped: [UI] Search/find didn't surface the freshly created file</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:34 (3.40s)</t>
+          <t>2026-06-18 10:17:16 (3.31s)</t>
         </is>
       </c>
     </row>
@@ -9070,19 +9180,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K34" s="104" t="inlineStr">
+      <c r="K34" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L34" s="105" t="inlineStr">
+      <c r="L34" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:35 (1.11s)</t>
+          <t>2026-06-18 10:17:17 (0.98s)</t>
         </is>
       </c>
     </row>
@@ -9129,19 +9239,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K35" s="104" t="inlineStr">
+      <c r="K35" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L35" s="105" t="inlineStr">
+      <c r="L35" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M35" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:40 (1.08s)</t>
+          <t>2026-06-18 10:37:17 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -9188,19 +9298,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K36" s="104" t="inlineStr">
+      <c r="K36" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L36" s="105" t="inlineStr">
+      <c r="L36" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M36" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:41 (1.02s)</t>
+          <t>2026-06-18 10:37:18 (0.94s)</t>
         </is>
       </c>
     </row>
@@ -9247,19 +9357,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K37" s="104" t="inlineStr">
+      <c r="K37" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L37" s="105" t="inlineStr">
+      <c r="L37" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:42 (1.05s)</t>
+          <t>2026-06-18 10:37:19 (0.86s)</t>
         </is>
       </c>
     </row>
@@ -9306,19 +9416,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K38" s="104" t="inlineStr">
+      <c r="K38" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L38" s="105" t="inlineStr">
+      <c r="L38" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:43 (1.05s)</t>
+          <t>2026-06-18 10:37:20 (1.00s)</t>
         </is>
       </c>
     </row>
@@ -9365,19 +9475,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K39" s="106" t="inlineStr">
+      <c r="K39" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L39" s="107" t="inlineStr">
+      <c r="L39" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'csv' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M39" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:43 (0.00s)</t>
+          <t>2026-06-18 10:37:20 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -9424,19 +9534,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K40" s="104" t="inlineStr">
+      <c r="K40" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L40" s="105" t="inlineStr">
+      <c r="L40" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M40" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:44 (1.01s)</t>
+          <t>2026-06-18 10:37:21 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -9483,19 +9593,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K41" s="104" t="inlineStr">
+      <c r="K41" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L41" s="105" t="inlineStr">
+      <c r="L41" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M41" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:45 (1.00s)</t>
+          <t>2026-06-18 10:37:22 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -9542,19 +9652,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K42" s="104" t="inlineStr">
+      <c r="K42" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L42" s="105" t="inlineStr">
+      <c r="L42" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M42" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:46 (1.08s)</t>
+          <t>2026-06-18 10:37:23 (0.99s)</t>
         </is>
       </c>
     </row>
@@ -9601,19 +9711,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K43" s="104" t="inlineStr">
+      <c r="K43" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L43" s="105" t="inlineStr">
+      <c r="L43" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M43" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:48 (1.10s)</t>
+          <t>2026-06-18 10:37:24 (1.10s)</t>
         </is>
       </c>
     </row>
@@ -9660,19 +9770,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K44" s="106" t="inlineStr">
+      <c r="K44" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L44" s="107" t="inlineStr">
+      <c r="L44" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'xml' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M44" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:48 (0.26s)</t>
+          <t>2026-06-18 10:37:24 (0.28s)</t>
         </is>
       </c>
     </row>
@@ -9719,19 +9829,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K45" s="104" t="inlineStr">
+      <c r="K45" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L45" s="105" t="inlineStr">
+      <c r="L45" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M45" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:49 (0.97s)</t>
+          <t>2026-06-18 10:37:25 (0.99s)</t>
         </is>
       </c>
     </row>
@@ -9778,19 +9888,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K46" s="104" t="inlineStr">
+      <c r="K46" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L46" s="105" t="inlineStr">
+      <c r="L46" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M46" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:50 (1.02s)</t>
+          <t>2026-06-18 10:37:26 (0.92s)</t>
         </is>
       </c>
     </row>
@@ -9837,19 +9947,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K47" s="106" t="inlineStr">
+      <c r="K47" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L47" s="107" t="inlineStr">
+      <c r="L47" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'rar' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M47" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:50 (0.00s)</t>
+          <t>2026-06-18 10:37:26 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -9896,19 +10006,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K48" s="104" t="inlineStr">
+      <c r="K48" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L48" s="105" t="inlineStr">
+      <c r="L48" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M48" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:51 (1.09s)</t>
+          <t>2026-06-18 10:37:27 (1.06s)</t>
         </is>
       </c>
     </row>
@@ -9955,19 +10065,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K49" s="106" t="inlineStr">
+      <c r="K49" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L49" s="107" t="inlineStr">
+      <c r="L49" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'tar' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M49" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:52 (1.32s)</t>
+          <t>2026-06-18 10:37:29 (1.26s)</t>
         </is>
       </c>
     </row>
@@ -10014,19 +10124,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K50" s="104" t="inlineStr">
+      <c r="K50" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L50" s="105" t="inlineStr">
+      <c r="L50" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M50" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:53 (1.12s)</t>
+          <t>2026-06-18 10:37:30 (0.94s)</t>
         </is>
       </c>
     </row>
@@ -10073,19 +10183,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K51" s="104" t="inlineStr">
+      <c r="K51" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L51" s="105" t="inlineStr">
+      <c r="L51" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M51" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:55 (1.11s)</t>
+          <t>2026-06-18 10:37:31 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -10132,19 +10242,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K52" s="104" t="inlineStr">
+      <c r="K52" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L52" s="105" t="inlineStr">
+      <c r="L52" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M52" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:56 (0.96s)</t>
+          <t>2026-06-18 10:37:32 (1.07s)</t>
         </is>
       </c>
     </row>
@@ -10191,19 +10301,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K53" s="104" t="inlineStr">
+      <c r="K53" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L53" s="105" t="inlineStr">
+      <c r="L53" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M53" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:56 (0.95s)</t>
+          <t>2026-06-18 10:37:33 (0.87s)</t>
         </is>
       </c>
     </row>
@@ -10250,19 +10360,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K54" s="104" t="inlineStr">
+      <c r="K54" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L54" s="105" t="inlineStr">
+      <c r="L54" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M54" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:57 (0.95s)</t>
+          <t>2026-06-18 10:37:34 (0.96s)</t>
         </is>
       </c>
     </row>
@@ -10309,19 +10419,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K55" s="106" t="inlineStr">
+      <c r="K55" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L55" s="107" t="inlineStr">
+      <c r="L55" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'tif' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M55" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:58 (0.19s)</t>
+          <t>2026-06-18 10:37:34 (0.25s)</t>
         </is>
       </c>
     </row>
@@ -10368,19 +10478,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K56" s="104" t="inlineStr">
+      <c r="K56" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L56" s="105" t="inlineStr">
+      <c r="L56" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M56" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:45:59 (1.07s)</t>
+          <t>2026-06-18 10:37:35 (0.99s)</t>
         </is>
       </c>
     </row>
@@ -10427,19 +10537,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K57" s="104" t="inlineStr">
+      <c r="K57" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L57" s="105" t="inlineStr">
+      <c r="L57" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M57" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:00 (0.92s)</t>
+          <t>2026-06-18 10:37:36 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -10486,19 +10596,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K58" s="104" t="inlineStr">
+      <c r="K58" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L58" s="105" t="inlineStr">
+      <c r="L58" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M58" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:01 (1.01s)</t>
+          <t>2026-06-18 10:37:37 (0.93s)</t>
         </is>
       </c>
     </row>
@@ -10545,19 +10655,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K59" s="106" t="inlineStr">
+      <c r="K59" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L59" s="107" t="inlineStr">
+      <c r="L59" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'wav' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M59" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:01 (0.00s)</t>
+          <t>2026-06-18 10:37:37 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -10604,19 +10714,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K60" s="104" t="inlineStr">
+      <c r="K60" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L60" s="105" t="inlineStr">
+      <c r="L60" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M60" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:02 (1.07s)</t>
+          <t>2026-06-18 10:37:38 (0.98s)</t>
         </is>
       </c>
     </row>
@@ -10663,19 +10773,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K61" s="106" t="inlineStr">
+      <c r="K61" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L61" s="107" t="inlineStr">
+      <c r="L61" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'flac' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M61" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:02 (0.00s)</t>
+          <t>2026-06-18 10:37:38 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -10722,19 +10832,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K62" s="104" t="inlineStr">
+      <c r="K62" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L62" s="105" t="inlineStr">
+      <c r="L62" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M62" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:03 (1.14s)</t>
+          <t>2026-06-18 10:37:39 (1.19s)</t>
         </is>
       </c>
     </row>
@@ -10781,19 +10891,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K63" s="104" t="inlineStr">
+      <c r="K63" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L63" s="105" t="inlineStr">
+      <c r="L63" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M63" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:04 (1.11s)</t>
+          <t>2026-06-18 10:37:40 (1.05s)</t>
         </is>
       </c>
     </row>
@@ -10840,19 +10950,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K64" s="104" t="inlineStr">
+      <c r="K64" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L64" s="105" t="inlineStr">
+      <c r="L64" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M64" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:06 (1.86s)</t>
+          <t>2026-06-18 10:37:42 (1.76s)</t>
         </is>
       </c>
     </row>
@@ -10899,19 +11009,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K65" s="104" t="inlineStr">
+      <c r="K65" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L65" s="105" t="inlineStr">
+      <c r="L65" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M65" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:11 (4.83s)</t>
+          <t>2026-06-18 10:37:47 (4.69s)</t>
         </is>
       </c>
     </row>
@@ -10958,19 +11068,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K66" s="104" t="inlineStr">
+      <c r="K66" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L66" s="105" t="inlineStr">
+      <c r="L66" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M66" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:12 (1.20s)</t>
+          <t>2026-06-18 10:37:48 (1.09s)</t>
         </is>
       </c>
     </row>
@@ -11017,19 +11127,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K67" s="106" t="inlineStr">
+      <c r="K67" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L67" s="107" t="inlineStr">
+      <c r="L67" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'wmv' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M67" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:12 (0.27s)</t>
+          <t>2026-06-18 10:37:48 (0.27s)</t>
         </is>
       </c>
     </row>
@@ -11076,19 +11186,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K68" s="106" t="inlineStr">
+      <c r="K68" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L68" s="107" t="inlineStr">
+      <c r="L68" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key '3gpp' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M68" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:13 (0.79s)</t>
+          <t>2026-06-18 10:37:49 (0.75s)</t>
         </is>
       </c>
     </row>
@@ -11135,19 +11245,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K69" s="106" t="inlineStr">
+      <c r="K69" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L69" s="107" t="inlineStr">
+      <c r="L69" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'flv' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M69" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:46:13 (0.25s)</t>
+          <t>2026-06-18 10:37:49 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -11198,19 +11308,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K70" s="106" t="inlineStr">
+      <c r="K70" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L70" s="107" t="inlineStr">
+      <c r="L70" s="131" t="inlineStr">
         <is>
           <t>Skipped: Notification verification requires recipient session — out of scope for owner-only test framework</t>
         </is>
       </c>
       <c r="M70" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:35 (0.00s)</t>
+          <t>2026-06-18 10:17:17 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11257,19 +11367,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K71" s="104" t="inlineStr">
+      <c r="K71" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L71" s="105" t="inlineStr">
+      <c r="L71" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M71" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:36 (1.43s)</t>
+          <t>2026-06-18 10:17:18 (1.21s)</t>
         </is>
       </c>
     </row>
@@ -11316,19 +11426,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K72" s="104" t="inlineStr">
+      <c r="K72" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L72" s="105" t="inlineStr">
+      <c r="L72" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M72" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:37 (1.26s)</t>
+          <t>2026-06-18 10:17:19 (1.13s)</t>
         </is>
       </c>
     </row>
@@ -11375,19 +11485,19 @@
           <t>403 Forbidden – Access denied</t>
         </is>
       </c>
-      <c r="K73" s="106" t="inlineStr">
+      <c r="K73" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L73" s="107" t="inlineStr">
+      <c r="L73" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M73" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:37 (0.00s)</t>
+          <t>2026-06-18 10:17:19 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11434,19 +11544,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K74" s="106" t="inlineStr">
+      <c r="K74" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L74" s="107" t="inlineStr">
+      <c r="L74" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M74" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:37 (0.00s)</t>
+          <t>2026-06-18 10:17:19 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11493,19 +11603,19 @@
           <t>403 Forbidden – Access revoked</t>
         </is>
       </c>
-      <c r="K75" s="106" t="inlineStr">
+      <c r="K75" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L75" s="107" t="inlineStr">
+      <c r="L75" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M75" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:37 (0.00s)</t>
+          <t>2026-06-18 10:17:19 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11552,19 +11662,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K76" s="106" t="inlineStr">
+      <c r="K76" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L76" s="107" t="inlineStr">
+      <c r="L76" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M76" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:37 (0.00s)</t>
+          <t>2026-06-18 10:17:19 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11611,19 +11721,19 @@
           <t>404 Not Found – Resource missing</t>
         </is>
       </c>
-      <c r="K77" s="104" t="inlineStr">
+      <c r="K77" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L77" s="105" t="inlineStr">
+      <c r="L77" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M77" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:39 (1.16s)</t>
+          <t>2026-06-18 10:17:20 (1.16s)</t>
         </is>
       </c>
     </row>
@@ -11670,19 +11780,19 @@
           <t>403 Forbidden – User inactive</t>
         </is>
       </c>
-      <c r="K78" s="106" t="inlineStr">
+      <c r="K78" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L78" s="107" t="inlineStr">
+      <c r="L78" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M78" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:39 (0.00s)</t>
+          <t>2026-06-18 10:17:20 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11729,19 +11839,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K79" s="104" t="inlineStr">
+      <c r="K79" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L79" s="105" t="inlineStr">
+      <c r="L79" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M79" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:40 (1.07s)</t>
+          <t>2026-06-18 10:17:21 (0.98s)</t>
         </is>
       </c>
     </row>
@@ -11788,19 +11898,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K80" s="106" t="inlineStr">
+      <c r="K80" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L80" s="107" t="inlineStr">
+      <c r="L80" s="131" t="inlineStr">
         <is>
           <t>Skipped: Notification API/UI verification not implemented yet</t>
         </is>
       </c>
       <c r="M80" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:40 (0.00s)</t>
+          <t>2026-06-18 10:17:21 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11847,19 +11957,19 @@
           <t xml:space="preserve"> - </t>
         </is>
       </c>
-      <c r="K81" s="104" t="inlineStr">
+      <c r="K81" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L81" s="105" t="inlineStr">
+      <c r="L81" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M81" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:21:40 (0.22s)</t>
+          <t>2026-06-18 10:17:21 (0.21s)</t>
         </is>
       </c>
     </row>
@@ -11998,7 +12108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" bestFit="1" customWidth="1" style="29" min="1" max="1"/>
@@ -12091,8 +12201,6 @@
       </c>
       <c r="B7" s="49" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10" ht="15.5" customHeight="1" s="29">
       <c r="A10" s="54" t="inlineStr">
         <is>
@@ -12222,19 +12330,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:06:09 (4.15s)</t>
+          <t>2026-06-18 10:29:31 (14.90s)</t>
         </is>
       </c>
     </row>
@@ -12281,19 +12389,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:06:15 (5.45s)</t>
+          <t>2026-06-18 10:29:36 (4.74s)</t>
         </is>
       </c>
     </row>
@@ -12340,19 +12448,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:06:19 (4.32s)</t>
+          <t>2026-06-18 10:29:40 (4.22s)</t>
         </is>
       </c>
     </row>
@@ -12399,19 +12507,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:06:32 (12.20s)</t>
+          <t>2026-06-18 10:29:54 (13.50s)</t>
         </is>
       </c>
     </row>
@@ -12458,19 +12566,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:06:36 (4.72s)</t>
+          <t>2026-06-18 10:29:59 (4.79s)</t>
         </is>
       </c>
     </row>
@@ -12517,23 +12625,23 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:13 (36.22s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>2026-06-18 10:30:51 (52.57s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72.5" customHeight="1" s="29">
       <c r="A18" s="11" t="n"/>
       <c r="B18" s="11" t="inlineStr">
         <is>
@@ -12576,19 +12684,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="108" t="inlineStr">
+      <c r="K18" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L18" s="109" t="inlineStr">
+      <c r="L18" s="125" t="inlineStr">
         <is>
           <t>HTTP 200 OK | playwright._impl._errors.TimeoutError: Timeout 20000ms exceeded while waiting for event "response"</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:43 (30.03s)</t>
+          <t>2026-06-18 10:31:22 (30.30s)</t>
         </is>
       </c>
     </row>
@@ -12635,19 +12743,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:52 (9.48s)</t>
+          <t>2026-06-18 10:31:31 (9.77s)</t>
         </is>
       </c>
     </row>
@@ -12694,19 +12802,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:53 (0.31s)</t>
+          <t>2026-06-18 10:31:32 (0.35s)</t>
         </is>
       </c>
     </row>
@@ -12753,19 +12861,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K21" s="106" t="inlineStr">
+      <c r="K21" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L21" s="107" t="inlineStr">
+      <c r="L21" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_trash_10 | NOT TESTABLE on demand. A real 500 from the empty-trash backend cannot be forced from the test client without server fault injection. Covered indirectly by TC_09's invalid-id rejection.</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:53 (0.00s)</t>
+          <t>2026-06-18 10:31:32 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -12812,19 +12920,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="107" t="inlineStr">
+      <c r="L22" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_trash_11 | NOT TESTABLE reliably. Simulating a mid-request network disconnect / 408 from the client is non-deterministic in this harness.</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:53 (0.00s)</t>
+          <t>2026-06-18 10:31:32 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -12871,19 +12979,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K23" s="106" t="inlineStr">
+      <c r="K23" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L23" s="107" t="inlineStr">
+      <c r="L23" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_trash_12 | NOT TESTABLE as a failure. The restoreFiles endpoint is lenient — it returns 200 even for a non-existent file id (verified on the live build), so a restore-to-missing-location failure cannot be forced from the client. The happy-path restore is covered by TC_03/TC_04.</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:53 (0.00s)</t>
+          <t>2026-06-18 10:31:32 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -12930,15 +13038,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="105" t="inlineStr"/>
+      <c r="L24" s="130" t="inlineStr"/>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:07:54 (1.55s)</t>
+          <t>2026-06-18 10:31:34 (1.56s)</t>
         </is>
       </c>
     </row>
@@ -12985,19 +13093,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="104" t="inlineStr">
+      <c r="K25" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L25" s="105" t="inlineStr">
+      <c r="L25" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:05 (10.37s)</t>
+          <t>2026-06-18 10:31:44 (10.54s)</t>
         </is>
       </c>
     </row>
@@ -13044,15 +13152,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="105" t="inlineStr"/>
+      <c r="L26" s="130" t="inlineStr"/>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:08 (3.72s)</t>
+          <t>2026-06-18 10:31:48 (3.71s)</t>
         </is>
       </c>
     </row>
@@ -13099,19 +13207,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K27" s="104" t="inlineStr">
+      <c r="K27" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L27" s="105" t="inlineStr">
+      <c r="L27" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:13 (4.62s)</t>
+          <t>2026-06-18 10:31:52 (4.58s)</t>
         </is>
       </c>
     </row>
@@ -13158,19 +13266,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="105" t="inlineStr">
+      <c r="L28" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:24 (10.90s)</t>
+          <t>2026-06-18 10:32:15 (22.70s)</t>
         </is>
       </c>
     </row>
@@ -13217,19 +13325,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="105" t="inlineStr">
+      <c r="L29" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:24 (0.31s)</t>
+          <t>2026-06-18 10:32:16 (0.33s)</t>
         </is>
       </c>
     </row>
@@ -13276,19 +13384,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="105" t="inlineStr">
+      <c r="L30" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:36 (11.42s)</t>
+          <t>2026-06-18 10:32:27 (11.65s)</t>
         </is>
       </c>
     </row>
@@ -13335,19 +13443,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K31" s="104" t="inlineStr">
+      <c r="K31" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L31" s="105" t="inlineStr">
+      <c r="L31" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:47 (11.67s)</t>
+          <t>2026-06-18 10:32:39 (11.97s)</t>
         </is>
       </c>
     </row>
@@ -13394,19 +13502,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K32" s="104" t="inlineStr">
+      <c r="K32" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L32" s="105" t="inlineStr">
+      <c r="L32" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:08:59 (11.08s)</t>
+          <t>2026-06-18 10:33:02 (22.65s)</t>
         </is>
       </c>
     </row>
@@ -13453,19 +13561,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K33" s="104" t="inlineStr">
+      <c r="K33" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L33" s="105" t="inlineStr">
+      <c r="L33" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:09:12 (13.85s)</t>
+          <t>2026-06-18 10:33:16 (14.31s)</t>
         </is>
       </c>
     </row>
@@ -13484,8 +13592,6 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="11" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37" ht="15.5" customHeight="1" s="29">
       <c r="A37" s="51" t="inlineStr">
         <is>
@@ -13592,10 +13698,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15075,6 +15177,1867 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="16.08984375" customWidth="1" style="29" min="1" max="1"/>
+    <col width="18.453125" customWidth="1" style="29" min="2" max="2"/>
+    <col width="45.81640625" customWidth="1" style="29" min="3" max="3"/>
+    <col width="31.26953125" customWidth="1" style="29" min="4" max="4"/>
+    <col width="18.54296875" customWidth="1" style="29" min="5" max="5"/>
+    <col width="17.08984375" customWidth="1" style="29" min="6" max="6"/>
+    <col width="20" customWidth="1" style="29" min="7" max="7"/>
+    <col width="32.36328125" customWidth="1" style="29" min="8" max="8"/>
+    <col width="24.26953125" customWidth="1" style="29" min="9" max="9"/>
+    <col width="19.81640625" customWidth="1" style="29" min="10" max="10"/>
+    <col width="16.453125" customWidth="1" style="29" min="11" max="11"/>
+    <col width="20.08984375" customWidth="1" style="29" min="12" max="12"/>
+    <col width="6.54296875" customWidth="1" style="29" min="13" max="13"/>
+    <col width="8.7265625" customWidth="1" style="29" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="98" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="97" t="inlineStr">
+        <is>
+          <t>TeamSync v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="98" t="inlineStr">
+        <is>
+          <t>Module Name</t>
+        </is>
+      </c>
+      <c r="B2" s="97" t="inlineStr">
+        <is>
+          <t>Advance Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="98" t="inlineStr">
+        <is>
+          <t>Build Version</t>
+        </is>
+      </c>
+      <c r="B3" s="97" t="inlineStr">
+        <is>
+          <t>v1.0.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="98" t="inlineStr">
+        <is>
+          <t>Test Environment</t>
+        </is>
+      </c>
+      <c r="B4" s="97" t="inlineStr">
+        <is>
+          <t>http://frontdms-teamsync.apps.lab.ocp.lan/teamsync/home</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="98" t="inlineStr">
+        <is>
+          <t>Executed By</t>
+        </is>
+      </c>
+      <c r="B5" s="97" t="inlineStr">
+        <is>
+          <t>Ankit tiwari</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="98" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="98" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>Pre-condition</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>Post-condition</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I10" s="99" t="inlineStr">
+        <is>
+          <t>Manual Status</t>
+        </is>
+      </c>
+      <c r="J10" s="99" t="inlineStr">
+        <is>
+          <t>Status code</t>
+        </is>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L10" s="99" t="inlineStr">
+        <is>
+          <t>Script error</t>
+        </is>
+      </c>
+      <c r="M10" s="99" t="inlineStr">
+        <is>
+          <t>Time stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="100" t="inlineStr">
+        <is>
+          <t>ADVANCE SEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Open Advanced Search in User drive</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Verify user can open advanced search panel</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Search panel is accessible</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Panel should open</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K12" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="134" t="inlineStr"/>
+      <c r="M12" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:33:35 (2.26s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Close Panel by Clicking Outside</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Verify panel closes when clicking outside</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Advanced search panel is open</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Search panel is closed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Panel should close</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K13" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="134" t="inlineStr"/>
+      <c r="M13" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:33:40 (2.81s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Search with Type Only</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Verify search using only document type</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Files of selected type displayed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K14" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L14" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M14" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:33:49 (5.86s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Search with Type + Attribute</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Verify attribute-based search</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Amount=5000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Matching files displayed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K15" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M15" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:33:58 (5.96s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Search Using Tag</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Verify tag-based filtering</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tagged files displayed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K16" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M16" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:06 (5.81s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Search Using Created Date</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Verify created date filtering</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Valid dates</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Files in range displayed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K17" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M17" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:14 (5.43s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Search Using Modified Date</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Verify modified date filtering</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Valid dates</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Correct files displayed</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K18" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M18" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:23 (5.35s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Search Owned by Me</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Verify filtering for current user</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Only my files should be displayed. files displayed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M19" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:31 (5.39s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Search Owned by Others</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Verify filtering for other users</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Other users' files displayed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M20" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:38 (5.05s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Search Specific Person</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verify search for specific user</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>user123</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Files of that user displayed</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M21" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:47 (5.71s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Combination Filter (Type + Tag)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Verify multiple filters together</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Invoice + Finance</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Matching files displayed</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K22" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M22" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:34:56 (6.59s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Combination Filter (All Filters)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verify all filters together</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Valid inputs</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Intersection data displayed</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K23" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L23" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M23" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:07 (8.36s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reset Button Functionality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Verify reset clears all filters</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Active parameters set in panel</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Parameters cleared to default</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>All filters cleared</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="134" t="inlineStr"/>
+      <c r="M24" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:15 (4.78s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Search with Type Attribute (Shortcut File - Shared with Me)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Verify search works for shared files only after creating shortcut</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>User A shared file with attributes to User B</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Shortcut file target resolution verified</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Type: Invoice Attribute: Amount = 7000</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Without shortcut → File should NOT appear (as per system behavior) After shortcut → File should appear in search results</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L25" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: SRCH_ADV01_TC14 | Requires a cross-user fixture: User A shares a typed file with User B, then B creates a shortcut. No second-user/share fixture exists in this single-account test env.</t>
+        </is>
+      </c>
+      <c r="M25" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:15 (0.00s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Search with Type Attribute (Nested Folder)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verify search works for files stored inside nested folder structure</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nested indexing verified</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Type: Invoice Attribute: Amount = 9000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>File should be displayed in search results even if it is inside nested folders</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K26" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L26" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M26" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:23 (5.62s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC16</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Search with tag in share with other filter.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Verify system behavior, when user search with tag in Share with others</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Summary list populated</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tag Name</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>File Should be displayed</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L27" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] Could not open 'Shared With Others' context</t>
+        </is>
+      </c>
+      <c r="M27" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:37 (10.93s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Search with meta data in Trash</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Verify System behaviour, when user search in trash tab with meta data.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Trash records indexed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>attribute value</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>File should be displayed</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K28" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L28" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] Could not open Trash context</t>
+        </is>
+      </c>
+      <c r="M28" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:52 (11.20s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Verify independent value entry in attribute fields</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Verify that each attribute field accepts its own value independently</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Input states isolated</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A = Test1, B = Test2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Each attribute should retain its own value</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L29" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] Need a type with at least 2 attributes</t>
+        </is>
+      </c>
+      <c r="M29" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:55 (0.49s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Attribute Without Value</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Verify validation when attribute value is missing</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Validation state checked</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Select Type</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Validation message displayedORFile should be displayed</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L30" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M30" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:04 (5.52s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Invalid Attribute Value</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Verify invalid data handling</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Input bounds tested</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>@#$%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Proper validation or no crash</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L31" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M31" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:12 (5.59s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC21</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Invalid Date Range</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Verify start date greater than end date</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Date logical cross-check handled</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Date Range</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>The system should not allow the Start Date to be later than the End Date.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K32" s="137" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L32" s="138" t="inlineStr">
+        <is>
+          <t>playwright._impl._errors.Error: Locator.fill: Error: Element is not an &lt;input&gt;, &lt;textarea&gt;, &lt;select&gt; or [contenteditable] and does not have a role allowing [aria-readonly]</t>
+        </is>
+      </c>
+      <c r="M32" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:19 (3.29s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC22</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Future Date Selection</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Verify future date handling</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Calendar constraints verified</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Future date</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Validation or no results</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K33" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L33" s="134" t="inlineStr"/>
+      <c r="M33" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:25 (3.15s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Invalid Specific Person</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Verify invalid user input</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>User tracking exception handled</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>xyz123@ios.com</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No result / error shown</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L34" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M34" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:33 (5.09s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tag with No Data</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Verify unused tag behavior</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Unassigned tag checked</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EmptyTag</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>“No results found”</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L35" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M35" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:40 (5.00s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No Filter Applied</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Verify behavior when search clicked without filters</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Standard operational default checked</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Default results OR validation (as per system)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L36" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M36" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:46 (3.13s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Conflicting Filters</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Verify filters with no intersection</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Contradictory filtering evaluated</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Random combination</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No results found</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K37" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L37" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M37" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:36:55 (5.97s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Large Data Stress</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Verify system behavior under heavy load</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High file volume present in target</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Performance stability confirmed</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>System should not crash</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L38" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M38" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:37:00 (2.53s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Verify value is not applied to all attribute fields</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Verify system does not auto-fill all attributes when value is entered in one field</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Input isolation confirmed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>A = Test1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Only Attribute A should have value; other fields should remain empty</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L39" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] Need a type with at least 2 attributes</t>
+        </is>
+      </c>
+      <c r="M39" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:37:03 (0.50s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="J42" s="76" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="J43" s="76" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Passed Test Cases</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Passed Test Cases</t>
+        </is>
+      </c>
+      <c r="J44" s="76" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Failed Test Cases</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Failed Test Cases</t>
+        </is>
+      </c>
+      <c r="J45" s="76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Blocked Test Cases</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Blocked Test Cases</t>
+        </is>
+      </c>
+      <c r="J46" s="76" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Not Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Not Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="J47" s="76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15307,19 +17270,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="110" t="inlineStr">
+      <c r="L14" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:13 (2.36s)</t>
+          <t>2026-06-18 10:06:00 (6.99s)</t>
         </is>
       </c>
     </row>
@@ -15366,19 +17329,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:16 (1.19s)</t>
+          <t>2026-06-18 10:06:02 (0.85s)</t>
         </is>
       </c>
     </row>
@@ -15425,19 +17388,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:18 (0.98s)</t>
+          <t>2026-06-18 10:06:04 (0.74s)</t>
         </is>
       </c>
     </row>
@@ -15484,19 +17447,19 @@
           <t xml:space="preserve"> - </t>
         </is>
       </c>
-      <c r="K17" s="106" t="inlineStr">
+      <c r="K17" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L17" s="111" t="inlineStr">
+      <c r="L17" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Login_04 | BLOCKED: 'Remember Me' checkbox not in current UI — inspect DOM and update selector in login_page.py</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:20 (0.00s)</t>
+          <t>2026-06-18 10:06:05 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -15543,19 +17506,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="110" t="inlineStr">
+      <c r="L18" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:23 (2.69s)</t>
+          <t>2026-06-18 10:06:07 (2.16s)</t>
         </is>
       </c>
     </row>
@@ -15602,19 +17565,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K19" s="108" t="inlineStr">
+      <c r="K19" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L19" s="112" t="inlineStr">
+      <c r="L19" s="125" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 401, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:33 (0.11s)</t>
+          <t>2026-06-18 10:06:17 (0.12s)</t>
         </is>
       </c>
     </row>
@@ -15661,19 +17624,19 @@
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="110" t="inlineStr">
+      <c r="L20" s="121" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:37 (3.88s)</t>
+          <t>2026-06-18 10:06:21 (3.60s)</t>
         </is>
       </c>
     </row>
@@ -15720,19 +17683,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="110" t="inlineStr">
+      <c r="L21" s="121" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:45 (8.17s)</t>
+          <t>2026-06-18 10:06:24 (2.58s)</t>
         </is>
       </c>
     </row>
@@ -15779,19 +17742,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="108" t="inlineStr">
+      <c r="K22" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L22" s="112" t="inlineStr">
+      <c r="L22" s="125" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 400, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:45 (0.12s)</t>
+          <t>2026-06-18 10:06:24 (0.09s)</t>
         </is>
       </c>
     </row>
@@ -15838,19 +17801,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="110" t="inlineStr">
+      <c r="L23" s="121" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:09:53 (7.88s)</t>
+          <t>2026-06-18 10:06:26 (2.56s)</t>
         </is>
       </c>
     </row>
@@ -15897,19 +17860,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="110" t="inlineStr">
+      <c r="L24" s="121" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:01 (8.06s)</t>
+          <t>2026-06-18 10:06:29 (2.57s)</t>
         </is>
       </c>
     </row>
@@ -15956,19 +17919,19 @@
           <t>423 Locked</t>
         </is>
       </c>
-      <c r="K25" s="106" t="inlineStr">
+      <c r="K25" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L25" s="111" t="inlineStr">
+      <c r="L25" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Login_12 | BLOCKED: No locked account in test env — create one and update LOCKED_USER</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:01 (0.00s)</t>
+          <t>2026-06-18 10:06:29 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16015,19 +17978,19 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="110" t="inlineStr">
+      <c r="L26" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:10 (9.07s)</t>
+          <t>2026-06-18 10:06:32 (3.65s)</t>
         </is>
       </c>
     </row>
@@ -16074,15 +18037,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K27" s="104" t="inlineStr">
+      <c r="K27" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L27" s="110" t="inlineStr"/>
+      <c r="L27" s="121" t="inlineStr"/>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:15 (0.49s)</t>
+          <t>2026-06-18 10:06:33 (0.37s)</t>
         </is>
       </c>
     </row>
@@ -16129,15 +18092,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="110" t="inlineStr"/>
+      <c r="L28" s="121" t="inlineStr"/>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:15 (0.32s)</t>
+          <t>2026-06-18 10:06:34 (0.33s)</t>
         </is>
       </c>
     </row>
@@ -16184,15 +18147,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="110" t="inlineStr"/>
+      <c r="L29" s="121" t="inlineStr"/>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:15 (0.29s)</t>
+          <t>2026-06-18 10:06:34 (0.32s)</t>
         </is>
       </c>
     </row>
@@ -16239,15 +18202,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="110" t="inlineStr"/>
+      <c r="L30" s="121" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:18 (2.38s)</t>
+          <t>2026-06-18 10:06:35 (0.95s)</t>
         </is>
       </c>
     </row>
@@ -16294,19 +18257,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K31" s="108" t="inlineStr">
+      <c r="K31" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L31" s="112" t="inlineStr">
+      <c r="L31" s="125" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 401, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:18 (0.21s)</t>
+          <t>2026-06-18 10:06:35 (0.13s)</t>
         </is>
       </c>
     </row>
@@ -16353,19 +18316,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K32" s="104" t="inlineStr">
+      <c r="K32" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L32" s="110" t="inlineStr">
+      <c r="L32" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:25 (6.53s)</t>
+          <t>2026-06-18 10:06:36 (0.83s)</t>
         </is>
       </c>
     </row>
@@ -16528,12 +18491,12 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="25" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.54296875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="40.6328125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="26.81640625" customWidth="1" style="1" min="2" max="2"/>
     <col width="20.54296875" bestFit="1" customWidth="1" style="41" min="3" max="3"/>
     <col width="41.6328125" bestFit="1" customWidth="1" style="41" min="4" max="4"/>
     <col width="26.36328125" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
     <col width="27.54296875" bestFit="1" customWidth="1" style="41" min="6" max="6"/>
-    <col width="45.7265625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="30.81640625" customWidth="1" style="1" min="7" max="7"/>
     <col width="38.90625" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
     <col width="14" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
     <col width="28.1796875" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
@@ -16541,8 +18504,8 @@
     <col width="47" bestFit="1" customWidth="1" style="41" min="12" max="12"/>
     <col width="26.26953125" bestFit="1" customWidth="1" style="1" min="13" max="13"/>
     <col width="25" customWidth="1" style="29" min="14" max="14"/>
-    <col width="25" customWidth="1" style="1" min="15" max="23"/>
-    <col width="25" customWidth="1" style="1" min="24" max="16384"/>
+    <col width="25" customWidth="1" style="1" min="15" max="27"/>
+    <col width="25" customWidth="1" style="1" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1" s="29">
@@ -16760,19 +18723,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="113" t="inlineStr">
+      <c r="L12" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:10:58 (21.35s)</t>
+          <t>2026-06-18 10:06:58 (8.07s)</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -16825,19 +18788,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="113" t="inlineStr">
+      <c r="L13" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:11:06 (8.14s)</t>
+          <t>2026-06-18 10:07:06 (7.91s)</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -16890,19 +18853,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="113" t="inlineStr">
+      <c r="L14" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:11:14 (8.15s)</t>
+          <t>2026-06-18 10:07:14 (7.96s)</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -16955,19 +18918,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="113" t="inlineStr">
+      <c r="L15" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:11:31 (16.86s)</t>
+          <t>2026-06-18 10:07:22 (8.06s)</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -17020,19 +18983,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="113" t="inlineStr">
+      <c r="L16" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:11:39 (8.10s)</t>
+          <t>2026-06-18 10:07:30 (8.04s)</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -17080,19 +19043,19 @@
           <t>If fails → Upload failed. Please try again</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="113" t="inlineStr">
+      <c r="L17" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:11:56 (16.97s)</t>
+          <t>2026-06-18 10:07:47 (16.94s)</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -17140,19 +19103,19 @@
           <t>If rejected → "File size exceeds limit" (incorrect behavior)</t>
         </is>
       </c>
-      <c r="K18" s="108" t="inlineStr">
+      <c r="K18" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L18" s="114" t="inlineStr">
-        <is>
-          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for 480 MB file (within 500 MB limit), got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1513536767, limit: 1556938752)","serviceName":"DMS</t>
+      <c r="L18" s="127" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for 480 MB file (within 500 MB limit), got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1522568155, limit: 1556938752)","serviceName":"DMS</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:12:50 (53.28s)</t>
+          <t>2026-06-18 10:08:38 (51.72s)</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -17200,19 +19163,19 @@
           <t>If 0 KB → "File is empty"</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="113" t="inlineStr">
+      <c r="L19" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:12:57 (7.55s)</t>
+          <t>2026-06-18 10:08:46 (8.05s)</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -17260,19 +19223,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="113" t="inlineStr">
+      <c r="L20" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:13:14 (16.96s)</t>
+          <t>2026-06-18 10:09:04 (17.38s)</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -17320,19 +19283,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="113" t="inlineStr">
+      <c r="L21" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:13:31 (16.94s)</t>
+          <t>2026-06-18 10:09:21 (17.01s)</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -17380,19 +19343,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="113" t="inlineStr">
+      <c r="L22" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:13:49 (17.54s)</t>
+          <t>2026-06-18 10:09:38 (17.02s)</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -17440,19 +19403,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L23" s="113" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK</t>
+      <c r="K23" s="122" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L23" s="128" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | Skipped: [UI→API] Could not capture open response: Timeout 15000ms exceeded while waiting for event "response"</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:14:07 (18.06s)</t>
+          <t>2026-06-18 10:10:10 (31.87s)</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -17500,24 +19463,24 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L24" s="113" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK</t>
+      <c r="K24" s="122" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L24" s="128" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | Skipped: [UI] Could not find/select uploaded file 'India_Overview.docx' in manager</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:14:58 (51.41s)</t>
+          <t>2026-06-18 10:10:35 (25.01s)</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="29" customHeight="1" s="29">
       <c r="A25" s="72" t="n"/>
       <c r="B25" s="72" t="inlineStr">
         <is>
@@ -17560,19 +19523,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="106" t="inlineStr">
+      <c r="K25" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L25" s="115" t="inlineStr">
+      <c r="L25" s="128" t="inlineStr">
         <is>
           <t>HTTP 200 OK | Skipped: [UI] Could not find row for 'test.docx' in file manager</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:15:26 (27.24s)</t>
+          <t>2026-06-18 10:11:02 (26.94s)</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -17620,19 +19583,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="113" t="inlineStr">
+      <c r="L26" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:15:45 (18.96s)</t>
+          <t>2026-06-18 10:11:20 (18.69s)</t>
         </is>
       </c>
       <c r="N26" s="11" t="n"/>
@@ -17680,19 +19643,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K27" s="104" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L27" s="113" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK</t>
+      <c r="K27" s="124" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L27" s="127" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for 480 MB file (within 500 MB limit), got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1525091435, limit: 1556938752)","serviceName":"DMS</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:16:45 (60.69s)</t>
+          <t>2026-06-18 10:12:16 (55.16s)</t>
         </is>
       </c>
       <c r="N27" s="11" t="n"/>
@@ -17740,19 +19703,19 @@
           <t>415 Unsupported Media Type/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="113" t="inlineStr">
+      <c r="L28" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:16:47 (1.57s)</t>
+          <t>2026-06-18 10:12:18 (1.69s)</t>
         </is>
       </c>
       <c r="N28" s="11" t="n"/>
@@ -17800,19 +19763,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="113" t="inlineStr">
+      <c r="L29" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:16:47 (0.21s)</t>
+          <t>2026-06-18 10:12:18 (0.21s)</t>
         </is>
       </c>
       <c r="N29" s="11" t="n"/>
@@ -17860,15 +19823,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="113" t="inlineStr"/>
+      <c r="L30" s="126" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:16:57 (9.48s)</t>
+          <t>2026-06-18 10:12:27 (9.42s)</t>
         </is>
       </c>
       <c r="N30" s="11" t="n"/>
@@ -17916,19 +19879,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K31" s="108" t="inlineStr">
+      <c r="K31" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L31" s="114" t="inlineStr">
-        <is>
-          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for action='replace', got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1513536767, limit: 1556938752)","serviceName":"DMS</t>
+      <c r="L31" s="127" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for action='replace', got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1523814750, limit: 1556938752)","serviceName":"DMS</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:17:49 (52.22s)</t>
+          <t>2026-06-18 10:13:25 (57.25s)</t>
         </is>
       </c>
       <c r="N31" s="11" t="n"/>
@@ -17976,19 +19939,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K32" s="106" t="inlineStr">
+      <c r="K32" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L32" s="115" t="inlineStr">
+      <c r="L32" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_21 | BLOCKED: Preview selector unknown</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:17:49 (0.00s)</t>
+          <t>2026-06-18 10:13:25 (0.00s)</t>
         </is>
       </c>
       <c r="N32" s="11" t="n"/>
@@ -18036,19 +19999,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K33" s="106" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="L33" s="115" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | Skipped: [UI] No test*.docx row found in file manager</t>
+      <c r="K33" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L33" s="126" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:06 (16.91s)</t>
+          <t>2026-06-18 10:13:46 (21.36s)</t>
         </is>
       </c>
       <c r="N33" s="11" t="n"/>
@@ -18096,19 +20059,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K34" s="106" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="L34" s="115" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | Skipped: [UI] No test*.docx row found in file manager</t>
+      <c r="K34" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L34" s="126" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:23 (16.93s)</t>
+          <t>2026-06-18 10:14:07 (21.18s)</t>
         </is>
       </c>
       <c r="N34" s="11" t="n"/>
@@ -18156,19 +20119,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K35" s="104" t="inlineStr">
+      <c r="K35" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L35" s="113" t="inlineStr">
+      <c r="L35" s="126" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized</t>
         </is>
       </c>
       <c r="M35" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:23 (0.14s)</t>
+          <t>2026-06-18 10:14:07 (0.08s)</t>
         </is>
       </c>
       <c r="N35" s="11" t="n"/>
@@ -18216,19 +20179,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K36" s="104" t="inlineStr">
+      <c r="K36" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L36" s="113" t="inlineStr">
+      <c r="L36" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M36" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:43 (20.05s)</t>
+          <t>2026-06-18 10:14:27 (19.88s)</t>
         </is>
       </c>
       <c r="N36" s="11" t="n"/>
@@ -18276,19 +20239,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K37" s="104" t="inlineStr">
+      <c r="K37" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L37" s="113" t="inlineStr">
+      <c r="L37" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:45 (1.71s)</t>
+          <t>2026-06-18 10:14:30 (2.37s)</t>
         </is>
       </c>
       <c r="N37" s="11" t="n"/>
@@ -18336,19 +20299,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K38" s="104" t="inlineStr">
+      <c r="K38" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L38" s="113" t="inlineStr">
+      <c r="L38" s="126" t="inlineStr">
         <is>
           <t>HTTP 403 Forbidden</t>
         </is>
       </c>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:46 (0.24s)</t>
+          <t>2026-06-18 10:14:30 (0.23s)</t>
         </is>
       </c>
       <c r="N38" s="11" t="n"/>
@@ -18396,19 +20359,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K39" s="104" t="inlineStr">
+      <c r="K39" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L39" s="113" t="inlineStr">
+      <c r="L39" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M39" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:46 (0.24s)</t>
+          <t>2026-06-18 10:14:31 (0.23s)</t>
         </is>
       </c>
       <c r="N39" s="11" t="n"/>
@@ -18456,19 +20419,19 @@
           <t xml:space="preserve"> Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K40" s="104" t="inlineStr">
+      <c r="K40" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L40" s="113" t="inlineStr">
+      <c r="L40" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M40" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:46 (0.25s)</t>
+          <t>2026-06-18 10:14:31 (0.34s)</t>
         </is>
       </c>
       <c r="N40" s="11" t="n"/>
@@ -18516,19 +20479,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K41" s="104" t="inlineStr">
+      <c r="K41" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L41" s="113" t="inlineStr">
+      <c r="L41" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M41" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:47 (0.21s)</t>
+          <t>2026-06-18 10:14:31 (0.20s)</t>
         </is>
       </c>
       <c r="N41" s="11" t="n"/>
@@ -18577,19 +20540,19 @@
 </t>
         </is>
       </c>
-      <c r="K42" s="104" t="inlineStr">
+      <c r="K42" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L42" s="113" t="inlineStr">
+      <c r="L42" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M42" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:47 (0.24s)</t>
+          <t>2026-06-18 10:14:32 (0.20s)</t>
         </is>
       </c>
       <c r="N42" s="11" t="n"/>
@@ -18637,19 +20600,19 @@
           <t>/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K43" s="104" t="inlineStr">
+      <c r="K43" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L43" s="113" t="inlineStr">
+      <c r="L43" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M43" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:49 (1.77s)</t>
+          <t>2026-06-18 10:14:33 (1.70s)</t>
         </is>
       </c>
       <c r="N43" s="11" t="n"/>
@@ -18697,19 +20660,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K44" s="104" t="inlineStr">
+      <c r="K44" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L44" s="113" t="inlineStr">
+      <c r="L44" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M44" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:51 (1.66s)</t>
+          <t>2026-06-18 10:14:36 (1.91s)</t>
         </is>
       </c>
       <c r="N44" s="11" t="n"/>
@@ -18757,19 +20720,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K45" s="106" t="inlineStr">
+      <c r="K45" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L45" s="115" t="inlineStr">
+      <c r="L45" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_34 | BLOCKED: Requires custom MIME header crafting</t>
         </is>
       </c>
       <c r="M45" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:51 (0.00s)</t>
+          <t>2026-06-18 10:14:36 (0.00s)</t>
         </is>
       </c>
       <c r="N45" s="11" t="n"/>
@@ -18817,19 +20780,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K46" s="106" t="inlineStr">
+      <c r="K46" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L46" s="115" t="inlineStr">
+      <c r="L46" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_35 | BLOCKED: Need an encrypted test file</t>
         </is>
       </c>
       <c r="M46" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:51 (0.00s)</t>
+          <t>2026-06-18 10:14:36 (0.00s)</t>
         </is>
       </c>
       <c r="N46" s="11" t="n"/>
@@ -18877,19 +20840,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K47" s="106" t="inlineStr">
+      <c r="K47" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L47" s="115" t="inlineStr">
+      <c r="L47" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_36 | BLOCKED: Need a password-protected PDF</t>
         </is>
       </c>
       <c r="M47" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:51 (0.00s)</t>
+          <t>2026-06-18 10:14:36 (0.00s)</t>
         </is>
       </c>
       <c r="N47" s="11" t="n"/>
@@ -18937,19 +20900,19 @@
           <t>200 OK / 415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K48" s="104" t="inlineStr">
+      <c r="K48" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L48" s="113" t="inlineStr">
+      <c r="L48" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M48" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:51 (0.40s)</t>
+          <t>2026-06-18 10:14:36 (0.38s)</t>
         </is>
       </c>
       <c r="N48" s="11" t="n"/>
@@ -18997,19 +20960,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K49" s="106" t="inlineStr">
+      <c r="K49" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L49" s="115" t="inlineStr">
+      <c r="L49" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_38 | BLOCKED: Need a nested ZIP test file</t>
         </is>
       </c>
       <c r="M49" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:51 (0.00s)</t>
+          <t>2026-06-18 10:14:36 (0.00s)</t>
         </is>
       </c>
       <c r="N49" s="11" t="n"/>
@@ -19057,19 +21020,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K50" s="104" t="inlineStr">
+      <c r="K50" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L50" s="113" t="inlineStr">
+      <c r="L50" s="126" t="inlineStr">
         <is>
           <t>HTTP 403 Forbidden</t>
         </is>
       </c>
       <c r="M50" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:52 (0.21s)</t>
+          <t>2026-06-18 10:14:36 (0.23s)</t>
         </is>
       </c>
       <c r="N50" s="11" t="n"/>
@@ -19117,19 +21080,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K51" s="104" t="inlineStr">
+      <c r="K51" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L51" s="113" t="inlineStr">
+      <c r="L51" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M51" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:52 (0.39s)</t>
+          <t>2026-06-18 10:14:37 (0.40s)</t>
         </is>
       </c>
       <c r="N51" s="11" t="n"/>
@@ -19177,19 +21140,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K52" s="106" t="inlineStr">
+      <c r="K52" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L52" s="115" t="inlineStr">
+      <c r="L52" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_41 | BLOCKED: Size limit unknown</t>
         </is>
       </c>
       <c r="M52" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:52 (0.00s)</t>
+          <t>2026-06-18 10:14:37 (0.00s)</t>
         </is>
       </c>
       <c r="N52" s="11" t="n"/>
@@ -19237,19 +21200,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K53" s="106" t="inlineStr">
+      <c r="K53" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L53" s="115" t="inlineStr">
+      <c r="L53" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_42 | BLOCKED: Size limit unknown</t>
         </is>
       </c>
       <c r="M53" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:52 (0.00s)</t>
+          <t>2026-06-18 10:14:37 (0.00s)</t>
         </is>
       </c>
       <c r="N53" s="11" t="n"/>
@@ -19297,19 +21260,19 @@
           <t>413 Payload Too Large/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K54" s="106" t="inlineStr">
+      <c r="K54" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L54" s="115" t="inlineStr">
+      <c r="L54" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_43 | BLOCKED: Creating very large files in CI is risky — run manually</t>
         </is>
       </c>
       <c r="M54" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:52 (0.00s)</t>
+          <t>2026-06-18 10:14:37 (0.00s)</t>
         </is>
       </c>
       <c r="N54" s="11" t="n"/>
@@ -19357,19 +21320,19 @@
           <t>400 Bad Request/415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K55" s="104" t="inlineStr">
+      <c r="K55" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L55" s="113" t="inlineStr">
+      <c r="L55" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M55" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:53 (0.22s)</t>
+          <t>2026-06-18 10:14:37 (0.21s)</t>
         </is>
       </c>
       <c r="N55" s="11" t="n"/>
@@ -19417,19 +21380,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K56" s="106" t="inlineStr">
+      <c r="K56" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L56" s="115" t="inlineStr">
+      <c r="L56" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_45 | BLOCKED: Size limit unknown</t>
         </is>
       </c>
       <c r="M56" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:53 (0.00s)</t>
+          <t>2026-06-18 10:14:37 (0.00s)</t>
         </is>
       </c>
       <c r="N56" s="11" t="n"/>
@@ -19477,19 +21440,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K57" s="106" t="inlineStr">
+      <c r="K57" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L57" s="115" t="inlineStr">
+      <c r="L57" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_46 | BLOCKED: Cannot simulate slow network in automated test</t>
         </is>
       </c>
       <c r="M57" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:18:53 (0.00s)</t>
+          <t>2026-06-18 10:14:37 (0.00s)</t>
         </is>
       </c>
       <c r="N57" s="11" t="n"/>
@@ -19537,19 +21500,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K58" s="104" t="inlineStr">
+      <c r="K58" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L58" s="113" t="inlineStr">
+      <c r="L58" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M58" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:13 (19.96s)</t>
+          <t>2026-06-18 10:14:57 (19.93s)</t>
         </is>
       </c>
       <c r="N58" s="11" t="n"/>
@@ -19597,19 +21560,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K59" s="104" t="inlineStr">
+      <c r="K59" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L59" s="113" t="inlineStr">
+      <c r="L59" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M59" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:33 (19.91s)</t>
+          <t>2026-06-18 10:15:17 (19.89s)</t>
         </is>
       </c>
       <c r="N59" s="11" t="n"/>
@@ -19657,19 +21620,19 @@
           <t>Uplaod Successfully</t>
         </is>
       </c>
-      <c r="K60" s="106" t="inlineStr">
+      <c r="K60" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L60" s="115" t="inlineStr">
+      <c r="L60" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_49 | KNOWN FAIL: Excel marks as FAIL — IMIR does not support resume upload</t>
         </is>
       </c>
       <c r="M60" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:33 (0.00s)</t>
+          <t>2026-06-18 10:15:17 (0.00s)</t>
         </is>
       </c>
       <c r="N60" s="11" t="n"/>
@@ -19717,19 +21680,19 @@
           <t>200/400</t>
         </is>
       </c>
-      <c r="K61" s="104" t="inlineStr">
+      <c r="K61" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L61" s="116" t="inlineStr">
+      <c r="L61" s="129" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M61" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:33 (0.47s)</t>
+          <t>2026-06-18 10:15:18 (0.43s)</t>
         </is>
       </c>
       <c r="N61" s="11" t="n"/>
@@ -19777,19 +21740,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K62" s="104" t="inlineStr">
+      <c r="K62" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L62" s="113" t="inlineStr">
+      <c r="L62" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M62" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:34 (0.44s)</t>
+          <t>2026-06-18 10:15:18 (0.42s)</t>
         </is>
       </c>
       <c r="N62" s="11" t="n"/>
@@ -19837,19 +21800,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K63" s="104" t="inlineStr">
+      <c r="K63" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L63" s="113" t="inlineStr">
+      <c r="L63" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M63" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:34 (0.26s)</t>
+          <t>2026-06-18 10:15:19 (0.23s)</t>
         </is>
       </c>
       <c r="N63" s="11" t="n"/>
@@ -19897,19 +21860,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K64" s="104" t="inlineStr">
+      <c r="K64" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L64" s="113" t="inlineStr">
+      <c r="L64" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M64" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:35 (0.44s)</t>
+          <t>2026-06-18 10:15:19 (0.39s)</t>
         </is>
       </c>
       <c r="N64" s="11" t="n"/>
@@ -19957,19 +21920,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K65" s="104" t="inlineStr">
+      <c r="K65" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L65" s="113" t="inlineStr">
+      <c r="L65" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M65" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:35 (0.45s)</t>
+          <t>2026-06-18 10:15:20 (0.43s)</t>
         </is>
       </c>
       <c r="N65" s="11" t="n"/>
@@ -20017,19 +21980,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K66" s="104" t="inlineStr">
+      <c r="K66" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L66" s="113" t="inlineStr">
+      <c r="L66" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M66" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:36 (0.45s)</t>
+          <t>2026-06-18 10:15:20 (0.42s)</t>
         </is>
       </c>
       <c r="N66" s="11" t="n"/>
@@ -20077,19 +22040,19 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="K67" s="104" t="inlineStr">
+      <c r="K67" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L67" s="113" t="inlineStr">
+      <c r="L67" s="126" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M67" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:37 (0.70s)</t>
+          <t>2026-06-18 10:15:21 (0.72s)</t>
         </is>
       </c>
       <c r="N67" s="11" t="n"/>
@@ -20137,15 +22100,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K68" s="104" t="inlineStr">
+      <c r="K68" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L68" s="113" t="inlineStr"/>
+      <c r="L68" s="126" t="inlineStr"/>
       <c r="M68" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:37 (0.01s)</t>
+          <t>2026-06-18 10:15:21 (0.02s)</t>
         </is>
       </c>
       <c r="N68" s="11" t="n"/>
@@ -20193,19 +22156,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K69" s="106" t="inlineStr">
+      <c r="K69" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L69" s="115" t="inlineStr">
+      <c r="L69" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_58 | KNOWN FAIL: Excel marks as FAIL — drag-and-drop returns 400, document as known bug</t>
         </is>
       </c>
       <c r="M69" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:37 (0.00s)</t>
+          <t>2026-06-18 10:15:21 (0.00s)</t>
         </is>
       </c>
       <c r="N69" s="11" t="n"/>
@@ -20253,19 +22216,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K70" s="106" t="inlineStr">
+      <c r="K70" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L70" s="115" t="inlineStr">
+      <c r="L70" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_59 | BLOCKED: Progress bar selector unknown — inspect upload dialog HTML</t>
         </is>
       </c>
       <c r="M70" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:37 (0.00s)</t>
+          <t>2026-06-18 10:15:21 (0.00s)</t>
         </is>
       </c>
       <c r="N70" s="11" t="n"/>
@@ -20313,15 +22276,15 @@
           <t>Canceled (client-side)</t>
         </is>
       </c>
-      <c r="K71" s="104" t="inlineStr">
+      <c r="K71" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L71" s="113" t="inlineStr"/>
+      <c r="L71" s="126" t="inlineStr"/>
       <c r="M71" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:40 (2.71s)</t>
+          <t>2026-06-18 10:15:24 (2.56s)</t>
         </is>
       </c>
       <c r="N71" s="11" t="n"/>
@@ -20369,19 +22332,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K72" s="106" t="inlineStr">
+      <c r="K72" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L72" s="115" t="inlineStr">
+      <c r="L72" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_61 | BLOCKED: Retry UI not identified</t>
         </is>
       </c>
       <c r="M72" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:40 (0.00s)</t>
+          <t>2026-06-18 10:15:24 (0.00s)</t>
         </is>
       </c>
       <c r="N72" s="11" t="n"/>
@@ -20429,19 +22392,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K73" s="104" t="inlineStr">
+      <c r="K73" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L73" s="113" t="inlineStr">
+      <c r="L73" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M73" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:19:42 (1.97s)</t>
+          <t>2026-06-18 10:15:26 (1.66s)</t>
         </is>
       </c>
       <c r="N73" s="11" t="n"/>
@@ -20489,19 +22452,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K74" s="104" t="inlineStr">
+      <c r="K74" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L74" s="113" t="inlineStr">
+      <c r="L74" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M74" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:20:02 (19.91s)</t>
+          <t>2026-06-18 10:15:46 (19.88s)</t>
         </is>
       </c>
       <c r="N74" s="11" t="n"/>
@@ -20549,19 +22512,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K75" s="104" t="inlineStr">
+      <c r="K75" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L75" s="113" t="inlineStr">
+      <c r="L75" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M75" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:20:22 (19.90s)</t>
+          <t>2026-06-18 10:16:06 (19.92s)</t>
         </is>
       </c>
       <c r="N75" s="11" t="n"/>
@@ -20609,19 +22572,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K76" s="104" t="inlineStr">
+      <c r="K76" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L76" s="113" t="inlineStr">
+      <c r="L76" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M76" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:20:49 (27.02s)</t>
+          <t>2026-06-18 10:16:32 (26.93s)</t>
         </is>
       </c>
       <c r="N76" s="11" t="n"/>
@@ -20669,19 +22632,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K77" s="106" t="inlineStr">
+      <c r="K77" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L77" s="115" t="inlineStr">
+      <c r="L77" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_66 | BLOCKED: Metadata API endpoint unknown</t>
         </is>
       </c>
       <c r="M77" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:20:49 (0.00s)</t>
+          <t>2026-06-18 10:16:32 (0.00s)</t>
         </is>
       </c>
       <c r="N77" s="11" t="n"/>
@@ -20729,19 +22692,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K78" s="106" t="inlineStr">
+      <c r="K78" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L78" s="115" t="inlineStr">
+      <c r="L78" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_67 | BLOCKED: Delete flow belongs to Delete module</t>
         </is>
       </c>
       <c r="M78" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:20:49 (0.00s)</t>
+          <t>2026-06-18 10:16:32 (0.00s)</t>
         </is>
       </c>
       <c r="N78" s="11" t="n"/>
@@ -20805,7 +22768,7 @@
         </is>
       </c>
       <c r="K83" s="75" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84">
@@ -20823,7 +22786,7 @@
         </is>
       </c>
       <c r="K84" s="75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -21093,19 +23056,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K8" s="108" t="inlineStr">
+      <c r="K8" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L8" s="112" t="inlineStr">
-        <is>
-          <t>AssertionError: [UI] Source file cpf_6a8f11ca.docx not in grid</t>
+      <c r="L8" s="125" t="inlineStr">
+        <is>
+          <t>AssertionError: [UI] Source file cpf_279f5cb6.docx not in grid</t>
         </is>
       </c>
       <c r="M8" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:55 (3.64s)</t>
+          <t>2026-06-18 10:22:24 (3.47s)</t>
         </is>
       </c>
       <c r="N8" s="84" t="n"/>
@@ -21158,19 +23121,19 @@
           <t>fail</t>
         </is>
       </c>
-      <c r="K9" s="104" t="inlineStr">
+      <c r="K9" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L9" s="110" t="inlineStr">
+      <c r="L9" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M9" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:57 (1.59s)</t>
+          <t>2026-06-18 10:22:26 (1.50s)</t>
         </is>
       </c>
       <c r="N9" s="84" t="n"/>
@@ -21223,19 +23186,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K10" s="106" t="inlineStr">
+      <c r="K10" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L10" s="111" t="inlineStr">
+      <c r="L10" s="123" t="inlineStr">
         <is>
           <t>Skipped: [SEED] No fixture files were available</t>
         </is>
       </c>
       <c r="M10" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:58 (0.57s)</t>
+          <t>2026-06-18 10:22:27 (0.61s)</t>
         </is>
       </c>
       <c r="N10" s="84" t="n"/>
@@ -21289,19 +23252,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K11" s="106" t="inlineStr">
+      <c r="K11" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L11" s="111" t="inlineStr">
+      <c r="L11" s="123" t="inlineStr">
         <is>
           <t>HTTP 200 OK | Skipped: [API] Download not 200 (src=400, dup=400)</t>
         </is>
       </c>
       <c r="M11" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:00 (1.83s)</t>
+          <t>2026-06-18 10:22:29 (1.87s)</t>
         </is>
       </c>
       <c r="N11" s="84" t="n"/>
@@ -21354,19 +23317,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="110" t="inlineStr">
+      <c r="L12" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:01 (1.42s)</t>
+          <t>2026-06-18 10:22:30 (1.47s)</t>
         </is>
       </c>
       <c r="N12" s="84" t="n"/>
@@ -21420,19 +23383,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="110" t="inlineStr">
+      <c r="L13" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:04 (3.00s)</t>
+          <t>2026-06-18 10:22:33 (2.72s)</t>
         </is>
       </c>
       <c r="N13" s="84" t="n"/>
@@ -21486,19 +23449,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="110" t="inlineStr">
+      <c r="L14" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:06 (2.15s)</t>
+          <t>2026-06-18 10:22:35 (1.95s)</t>
         </is>
       </c>
       <c r="N14" s="84" t="n"/>
@@ -21552,19 +23515,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:08 (1.77s)</t>
+          <t>2026-06-18 10:22:37 (1.84s)</t>
         </is>
       </c>
       <c r="N15" s="84" t="n"/>
@@ -21618,19 +23581,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:09 (1.13s)</t>
+          <t>2026-06-18 10:22:38 (1.04s)</t>
         </is>
       </c>
       <c r="N16" s="84" t="n"/>
@@ -21683,19 +23646,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K17" s="106" t="inlineStr">
+      <c r="K17" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L17" s="111" t="inlineStr">
+      <c r="L17" s="123" t="inlineStr">
         <is>
           <t>Skipped: Skipped per project decision — Syncfusion grid keyboard shortcut needs focus management not worth the complexity</t>
         </is>
       </c>
       <c r="M17" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:27:09 (0.00s)</t>
+          <t>2026-06-18 10:22:38 (0.00s)</t>
         </is>
       </c>
       <c r="N17" s="84" t="n"/>
@@ -21747,19 +23710,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K18" s="106" t="inlineStr">
+      <c r="K18" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L18" s="111" t="inlineStr">
+      <c r="L18" s="123" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Upload status 403 | body: {"error":"File type not allowed. Please contact the admin to allow this extension.","status":"FORBIDDEN"}</t>
         </is>
       </c>
       <c r="M18" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:33 (203.56s)</t>
+          <t>2026-06-18 10:25:26 (168.20s)</t>
         </is>
       </c>
       <c r="N18" s="84" t="n"/>
@@ -22115,19 +24078,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K12" s="108" t="inlineStr">
+      <c r="K12" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L12" s="112" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_3118a54c' did not appear in the file manager</t>
+      <c r="L12" s="125" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_659a9c0e' did not appear in the file manager</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:15 (21.38s)</t>
+          <t>2026-06-18 10:17:55 (21.19s)</t>
         </is>
       </c>
     </row>
@@ -22174,19 +24137,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="110" t="inlineStr">
+      <c r="L13" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:15 (0.30s)</t>
+          <t>2026-06-18 10:17:56 (0.29s)</t>
         </is>
       </c>
     </row>
@@ -22233,19 +24196,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="110" t="inlineStr">
+      <c r="L14" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:16 (0.94s)</t>
+          <t>2026-06-18 10:17:57 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -22292,19 +24255,19 @@
           <t>Handel from frontend.</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:17 (0.29s)</t>
+          <t>2026-06-18 10:17:57 (0.28s)</t>
         </is>
       </c>
     </row>
@@ -22351,19 +24314,19 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:17 (0.56s)</t>
+          <t>2026-06-18 10:17:58 (0.56s)</t>
         </is>
       </c>
     </row>
@@ -22410,19 +24373,19 @@
           <t>Handel from frontend(Folder name cannot be empty or just spaces)</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="110" t="inlineStr">
+      <c r="L17" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:21 (3.24s)</t>
+          <t>2026-06-18 10:18:01 (3.10s)</t>
         </is>
       </c>
     </row>
@@ -22469,19 +24432,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="110" t="inlineStr">
+      <c r="L18" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:21 (0.31s)</t>
+          <t>2026-06-18 10:18:02 (0.34s)</t>
         </is>
       </c>
     </row>
@@ -22528,19 +24491,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K19" s="106" t="inlineStr">
+      <c r="K19" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L19" s="111" t="inlineStr">
+      <c r="L19" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_08 | BLOCKED: Cannot reliably trigger 500 from a client test — requires server-side fault injection</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:21 (0.00s)</t>
+          <t>2026-06-18 10:18:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22587,19 +24550,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="110" t="inlineStr">
+      <c r="L20" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (7.97s)</t>
+          <t>2026-06-18 10:18:10 (7.80s)</t>
         </is>
       </c>
     </row>
@@ -22646,19 +24609,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="106" t="inlineStr">
+      <c r="K21" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L21" s="111" t="inlineStr">
+      <c r="L21" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_10 | BLOCKED: Need editor open cURL + iframe selector</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22705,19 +24668,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="111" t="inlineStr">
+      <c r="L22" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_11 | BLOCKED: Need editor input selector</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22764,19 +24727,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="106" t="inlineStr">
+      <c r="K23" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L23" s="111" t="inlineStr">
+      <c r="L23" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_12 | BLOCKED: Need autosave network call signature</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22823,19 +24786,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="106" t="inlineStr">
+      <c r="K24" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L24" s="111" t="inlineStr">
+      <c r="L24" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_13 | BLOCKED: Need Save button selector + cURL</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22882,19 +24845,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="106" t="inlineStr">
+      <c r="K25" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L25" s="111" t="inlineStr">
+      <c r="L25" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_14 | BLOCKED: Multi-session test — requires two parallel browser contexts</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22941,19 +24904,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="106" t="inlineStr">
+      <c r="K26" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L26" s="111" t="inlineStr">
+      <c r="L26" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_15 | BLOCKED: Need formatting toolbar selectors</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23000,19 +24963,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K27" s="106" t="inlineStr">
+      <c r="K27" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L27" s="111" t="inlineStr">
+      <c r="L27" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_16 | BLOCKED: Need insert-image button selector + cURL</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23059,19 +25022,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K28" s="106" t="inlineStr">
+      <c r="K28" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L28" s="111" t="inlineStr">
+      <c r="L28" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_17 | BLOCKED: Need Undo/Redo button selectors</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23118,19 +25081,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K29" s="106" t="inlineStr">
+      <c r="K29" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L29" s="111" t="inlineStr">
+      <c r="L29" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_18 | BLOCKED: Need fullscreen button selector</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23177,19 +25140,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="106" t="inlineStr">
+      <c r="K30" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L30" s="111" t="inlineStr">
+      <c r="L30" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_19 | BLOCKED: Need insert-table button selector</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23236,19 +25199,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K31" s="106" t="inlineStr">
+      <c r="K31" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L31" s="111" t="inlineStr">
+      <c r="L31" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_20 | BLOCKED: Need header button selector</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23295,19 +25258,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K32" s="106" t="inlineStr">
+      <c r="K32" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L32" s="111" t="inlineStr">
+      <c r="L32" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_21 | BLOCKED: Need footer button selector</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23354,19 +25317,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K33" s="106" t="inlineStr">
+      <c r="K33" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L33" s="111" t="inlineStr">
+      <c r="L33" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_22 | BLOCKED: Need print button + verification approach</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23413,19 +25376,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K34" s="106" t="inlineStr">
+      <c r="K34" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L34" s="111" t="inlineStr">
+      <c r="L34" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_23 | BLOCKED: Need editor copy/paste verification approach</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:29 (0.00s)</t>
+          <t>2026-06-18 10:18:10 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23775,19 +25738,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:58 (21.34s)</t>
+          <t>2026-06-18 10:25:59 (20.31s)</t>
         </is>
       </c>
     </row>
@@ -23834,19 +25797,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:32:10 (12.48s)</t>
+          <t>2026-06-18 10:26:09 (9.71s)</t>
         </is>
       </c>
     </row>
@@ -23893,19 +25856,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:34:00 (109.64s)</t>
+          <t>2026-06-18 10:27:50 (101.16s)</t>
         </is>
       </c>
     </row>
@@ -23952,19 +25915,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:34:12 (11.62s)</t>
+          <t>2026-06-18 10:28:02 (11.43s)</t>
         </is>
       </c>
     </row>
@@ -24007,19 +25970,19 @@
       </c>
       <c r="I16" s="73" t="n"/>
       <c r="J16" s="73" t="n"/>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:34:24 (11.81s)</t>
+          <t>2026-06-18 10:28:13 (11.31s)</t>
         </is>
       </c>
     </row>
@@ -24066,19 +26029,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:34:37 (13.90s)</t>
+          <t>2026-06-18 10:28:26 (13.34s)</t>
         </is>
       </c>
     </row>
@@ -24125,19 +26088,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:34:49 (11.61s)</t>
+          <t>2026-06-18 10:28:37 (11.27s)</t>
         </is>
       </c>
     </row>
@@ -24184,19 +26147,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:35:04 (15.10s)</t>
+          <t>2026-06-18 10:28:52 (14.25s)</t>
         </is>
       </c>
     </row>
@@ -24243,19 +26206,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:35:16 (11.77s)</t>
+          <t>2026-06-18 10:29:03 (11.43s)</t>
         </is>
       </c>
     </row>
@@ -24302,19 +26265,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr">
+      <c r="L21" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:35:16 (0.29s)</t>
+          <t>2026-06-18 10:29:04 (0.27s)</t>
         </is>
       </c>
     </row>
@@ -24361,19 +26324,19 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="107" t="inlineStr">
+      <c r="L22" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_delete_11 | NOT TESTABLE in current env. 'Shared With Me' exposes only a 'Remove Access' action — there is no Delete button on shared files. A true test needs a real shared-file fixture (a second user shares a file with this account), which the test environment does not provide.</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:35:16 (0.00s)</t>
+          <t>2026-06-18 10:29:04 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -24716,19 +26679,19 @@
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:22:57 (9.64s)</t>
+          <t>2026-06-18 10:18:36 (8.72s)</t>
         </is>
       </c>
     </row>
@@ -24775,19 +26738,19 @@
         </is>
       </c>
       <c r="J13" s="11" t="n"/>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:23:00 (2.54s)</t>
+          <t>2026-06-18 10:18:39 (2.24s)</t>
         </is>
       </c>
     </row>
@@ -24834,19 +26797,19 @@
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:23:10 (9.42s)</t>
+          <t>2026-06-18 10:18:48 (8.53s)</t>
         </is>
       </c>
     </row>
@@ -24893,19 +26856,19 @@
         </is>
       </c>
       <c r="J15" s="11" t="n"/>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:23:21 (9.94s)</t>
+          <t>2026-06-18 10:18:57 (8.47s)</t>
         </is>
       </c>
     </row>
@@ -24952,19 +26915,19 @@
         </is>
       </c>
       <c r="J16" s="11" t="n"/>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:23:33 (12.09s)</t>
+          <t>2026-06-18 10:19:09 (10.48s)</t>
         </is>
       </c>
     </row>
@@ -25011,19 +26974,19 @@
         </is>
       </c>
       <c r="J17" s="11" t="n"/>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:23:51 (17.17s)</t>
+          <t>2026-06-18 10:19:26 (16.28s)</t>
         </is>
       </c>
     </row>
@@ -25070,19 +27033,19 @@
         </is>
       </c>
       <c r="J18" s="11" t="n"/>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:24:09 (17.88s)</t>
+          <t>2026-06-18 10:19:42 (16.18s)</t>
         </is>
       </c>
     </row>
@@ -25129,19 +27092,19 @@
         </is>
       </c>
       <c r="J19" s="11" t="n"/>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:24:19 (9.59s)</t>
+          <t>2026-06-18 10:19:51 (9.23s)</t>
         </is>
       </c>
     </row>
@@ -25188,19 +27151,19 @@
         </is>
       </c>
       <c r="J20" s="11" t="n"/>
-      <c r="K20" s="106" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="L20" s="107" t="inlineStr">
-        <is>
-          <t>Skipped: [UI] Need &gt;=2 folders for the duplicate-name test</t>
+      <c r="K20" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="130" t="inlineStr">
+        <is>
+          <t>HTTP 409 Conflict</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:24:22 (3.60s)</t>
+          <t>2026-06-18 10:19:57 (4.61s)</t>
         </is>
       </c>
     </row>
@@ -25247,15 +27210,15 @@
         </is>
       </c>
       <c r="J21" s="11" t="n"/>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr"/>
+      <c r="L21" s="130" t="inlineStr"/>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:24:43 (20.52s)</t>
+          <t>2026-06-18 10:20:17 (19.97s)</t>
         </is>
       </c>
     </row>
@@ -25302,15 +27265,15 @@
         </is>
       </c>
       <c r="J22" s="11" t="n"/>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="105" t="inlineStr"/>
+      <c r="L22" s="130" t="inlineStr"/>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:25:04 (20.92s)</t>
+          <t>2026-06-18 10:20:37 (19.93s)</t>
         </is>
       </c>
     </row>
@@ -25357,19 +27320,19 @@
         </is>
       </c>
       <c r="J23" s="11" t="n"/>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="105" t="inlineStr">
+      <c r="L23" s="130" t="inlineStr">
         <is>
           <t>HTTP 0</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:25:14 (9.56s)</t>
+          <t>2026-06-18 10:20:45 (8.72s)</t>
         </is>
       </c>
     </row>
@@ -25416,19 +27379,19 @@
         </is>
       </c>
       <c r="J24" s="11" t="n"/>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="105" t="inlineStr">
+      <c r="L24" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:25:27 (12.52s)</t>
+          <t>2026-06-18 10:20:57 (11.04s)</t>
         </is>
       </c>
     </row>
@@ -25475,19 +27438,19 @@
         </is>
       </c>
       <c r="J25" s="11" t="n"/>
-      <c r="K25" s="104" t="inlineStr">
+      <c r="K25" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L25" s="105" t="inlineStr">
+      <c r="L25" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:25:50 (22.35s)</t>
+          <t>2026-06-18 10:21:19 (21.07s)</t>
         </is>
       </c>
     </row>
@@ -25529,7 +27492,7 @@
         </is>
       </c>
       <c r="J29" s="77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" ht="31" customHeight="1" s="29">
@@ -25545,7 +27508,7 @@
         </is>
       </c>
       <c r="J30" s="77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" s="29">
@@ -25577,7 +27540,7 @@
         </is>
       </c>
       <c r="J32" s="77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="31" customHeight="1" s="29">
@@ -25832,19 +27795,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="110" t="inlineStr">
+      <c r="L12" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:09 (0.37s)</t>
+          <t>2026-06-18 10:21:38 (0.42s)</t>
         </is>
       </c>
     </row>
@@ -25891,19 +27854,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="110" t="inlineStr">
+      <c r="L13" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:10 (0.29s)</t>
+          <t>2026-06-18 10:21:38 (0.28s)</t>
         </is>
       </c>
     </row>
@@ -25950,19 +27913,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="108" t="inlineStr">
+      <c r="K14" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L14" s="112" t="inlineStr">
+      <c r="L14" s="125" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request | AssertionError: [API] Expected 200, got 400</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:10 (0.34s)</t>
+          <t>2026-06-18 10:21:38 (0.31s)</t>
         </is>
       </c>
     </row>
@@ -26009,19 +27972,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:11 (0.50s)</t>
+          <t>2026-06-18 10:21:39 (0.34s)</t>
         </is>
       </c>
     </row>
@@ -26068,19 +28031,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:14 (3.18s)</t>
+          <t>2026-06-18 10:21:42 (3.18s)</t>
         </is>
       </c>
     </row>
@@ -26127,19 +28090,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="110" t="inlineStr">
+      <c r="L17" s="121" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:14 (0.67s)</t>
+          <t>2026-06-18 10:21:43 (0.65s)</t>
         </is>
       </c>
     </row>
@@ -26186,19 +28149,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="110" t="inlineStr">
+      <c r="L18" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:18 (3.60s)</t>
+          <t>2026-06-18 10:21:46 (3.61s)</t>
         </is>
       </c>
     </row>
@@ -26245,19 +28208,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="110" t="inlineStr">
+      <c r="L19" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:23 (5.03s)</t>
+          <t>2026-06-18 10:21:51 (5.21s)</t>
         </is>
       </c>
     </row>
@@ -26304,19 +28267,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="110" t="inlineStr">
+      <c r="L20" s="121" t="inlineStr">
         <is>
           <t>HTTP 0</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:29 (6.22s)</t>
+          <t>2026-06-18 10:21:58 (6.46s)</t>
         </is>
       </c>
     </row>
@@ -26363,19 +28326,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="110" t="inlineStr">
+      <c r="L21" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:35 (5.70s)</t>
+          <t>2026-06-18 10:22:04 (5.94s)</t>
         </is>
       </c>
     </row>
@@ -26422,19 +28385,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="110" t="inlineStr">
+      <c r="L22" s="121" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:35 (0.22s)</t>
+          <t>2026-06-18 10:22:04 (0.21s)</t>
         </is>
       </c>
     </row>
@@ -26481,19 +28444,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="108" t="inlineStr">
+      <c r="K23" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L23" s="112" t="inlineStr">
+      <c r="L23" s="125" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request | AssertionError: [API] Bulk move failed: 400</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:36 (0.33s)</t>
+          <t>2026-06-18 10:22:04 (0.38s)</t>
         </is>
       </c>
     </row>
@@ -26540,19 +28503,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="110" t="inlineStr">
+      <c r="L24" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:26:39 (3.04s)</t>
+          <t>2026-06-18 10:22:08 (3.19s)</t>
         </is>
       </c>
     </row>
@@ -26949,19 +28912,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:47 (0.55s)</t>
+          <t>2026-06-11 16:58:53 (0.54s)</t>
         </is>
       </c>
     </row>
@@ -27008,19 +28971,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:48 (1.00s)</t>
+          <t>2026-06-11 16:58:54 (0.79s)</t>
         </is>
       </c>
     </row>
@@ -27067,19 +29030,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:49 (1.06s)</t>
+          <t>2026-06-11 16:58:55 (0.92s)</t>
         </is>
       </c>
     </row>
@@ -27126,19 +29089,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:50 (1.83s)</t>
+          <t>2026-06-11 16:58:56 (1.58s)</t>
         </is>
       </c>
     </row>
@@ -27185,19 +29148,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:51 (0.84s)</t>
+          <t>2026-06-11 16:58:57 (0.72s)</t>
         </is>
       </c>
     </row>
@@ -27244,19 +29207,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:52 (0.77s)</t>
+          <t>2026-06-11 16:58:58 (0.75s)</t>
         </is>
       </c>
     </row>
@@ -27303,15 +29266,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr"/>
+      <c r="L18" s="92" t="n"/>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:53 (0.87s)</t>
+          <t>2026-06-11 16:58:58 (0.77s)</t>
         </is>
       </c>
     </row>
@@ -27358,19 +29321,19 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:55 (2.05s)</t>
+          <t>2026-06-11 16:59:00 (1.88s)</t>
         </is>
       </c>
     </row>
@@ -27417,19 +29380,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="92" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:56 (1.11s)</t>
+          <t>2026-06-11 16:59:01 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -27476,19 +29439,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr">
+      <c r="L21" s="92" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:56 (0.21s)</t>
+          <t>2026-06-11 16:59:01 (0.19s)</t>
         </is>
       </c>
     </row>
@@ -27535,19 +29498,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="93" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="107" t="inlineStr">
+      <c r="L22" s="94" t="inlineStr">
         <is>
           <t>Skipped: Can't simulate true network failure deterministically</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:30:56 (0.00s)</t>
+          <t>2026-06-11 16:59:01 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -27594,15 +29557,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="105" t="inlineStr"/>
+      <c r="L23" s="92" t="n"/>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:02 (5.93s)</t>
+          <t>2026-06-11 16:59:07 (5.49s)</t>
         </is>
       </c>
     </row>
@@ -27649,15 +29612,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="105" t="inlineStr"/>
+      <c r="L24" s="92" t="n"/>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:10 (7.61s)</t>
+          <t>2026-06-11 16:59:13 (6.08s)</t>
         </is>
       </c>
     </row>
@@ -27704,15 +29667,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="104" t="inlineStr">
+      <c r="K25" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L25" s="105" t="inlineStr"/>
+      <c r="L25" s="92" t="n"/>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:18 (8.02s)</t>
+          <t>2026-06-11 16:59:19 (6.03s)</t>
         </is>
       </c>
     </row>
@@ -27759,19 +29722,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="105" t="inlineStr">
+      <c r="L26" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:20 (1.83s)</t>
+          <t>2026-06-11 16:59:21 (1.70s)</t>
         </is>
       </c>
     </row>
@@ -27818,19 +29781,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K27" s="108" t="inlineStr">
+      <c r="K27" s="95" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L27" s="109" t="inlineStr">
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <t>HTTP 200 OK | AssertionError: [API] Expected 4xx/5xx for invalid file id, got 200</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:20 (0.24s)</t>
+          <t>2026-06-11 16:59:21 (0.20s)</t>
         </is>
       </c>
     </row>
@@ -27877,19 +29840,19 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="K28" s="106" t="inlineStr">
+      <c r="K28" s="93" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L28" s="107" t="inlineStr">
+      <c r="L28" s="94" t="inlineStr">
         <is>
           <t>Skipped: Requires a second user (owner) and a clear unshare API</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:20 (0.00s)</t>
+          <t>2026-06-11 16:59:21 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -27936,19 +29899,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="105" t="inlineStr">
+      <c r="L29" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:23 (3.18s)</t>
+          <t>2026-06-11 16:59:24 (2.70s)</t>
         </is>
       </c>
     </row>
@@ -27995,19 +29958,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K30" s="106" t="inlineStr">
+      <c r="K30" s="93" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L30" s="107" t="inlineStr">
+      <c r="L30" s="94" t="inlineStr">
         <is>
           <t>Skipped: Requires second + third user sessions to verify</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 15:31:23 (0.02s)</t>
+          <t>2026-06-11 16:59:24 (0.00s)</t>
         </is>
       </c>
     </row>
